--- a/hiedra-filosofas-mapa-listo.xlsx
+++ b/hiedra-filosofas-mapa-listo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nati\OneDrive\Escritorio\La_hiedra_en_la_grieta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FEE977-2B6D-49ED-92AE-F22A0C7ECD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40C5C96-0F24-4C85-8BA0-83EC6C8BB673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{710D68A0-BE3B-4DEE-ABF3-33E9BEF5963F}"/>
+    <workbookView xWindow="780" yWindow="255" windowWidth="19080" windowHeight="10545" xr2:uid="{710D68A0-BE3B-4DEE-ABF3-33E9BEF5963F}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapa" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="945">
   <si>
     <t>Fecha de nacimiento</t>
   </si>
@@ -436,9 +436,6 @@
     <t>https://www.youtube.com/watch?v=WDovm3A1wI4&amp;t=240s</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=MVZpoIz8ei4</t>
-  </si>
-  <si>
     <t>Situating the Self (1992), The Rights of Others (2000), The Claims of Culture (2002)</t>
   </si>
   <si>
@@ -550,9 +547,6 @@
     <t>https://seis-ucla-edu.translate.goog/faculty/sandra-harding/?_x_tr_sl=en&amp;_x_tr_tl=es&amp;_x_tr_hl=es&amp;_x_tr_pto=tc&amp;_x_tr_hist=true</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=1C2wRfup6sE</t>
-  </si>
-  <si>
     <t>https://bellhooksbooks.com/about-bell-hooks/</t>
   </si>
   <si>
@@ -812,12 +806,6 @@
   </si>
   <si>
     <t>http://www.alcoff.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/search?q=linda+martin+Alcoff+entrevista&amp;client=opera-gx&amp;hs=r5g&amp;sca_esv=e0a8504cdddaab2b&amp;biw=1324&amp;bih=611&amp;sxsrf=ANbL-n53WnxGOPJ37GWsJ12i1lc4WwDzyw%3A1773545143598&amp;ei=tya2afOaJMnY1sQP-qPK0AY&amp;ved=0ahUKEwiz0pvC-qCTAxVJrJUCHfqREmoQ4dUDCBM&amp;uact=5&amp;oq=linda+martin+Alcoff+entrevista&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiHmxpbmRhIG1hcnRpbiBBbGNvZmYgZW50cmV2aXN0YTIFECEYoAEyBRAhGKABMgUQIRigAUiXC1DIAlilCnABeACQAQCYAXmgAdEHqgEDOC4yuAEDyAEA-AEBmAIKoAKRB8ICCxAAGIAEGLADGKIEwgIIEAAYsAMY7wWYAwCIBgGQBgSSBwM3LjOgB-0ZsgcDNi4zuAeOB8IHBDAuMTDIBw6ACAA&amp;sclient=gws-wiz-serp#fpstate=ive&amp;vld=cid:59edc99d,vid:6y2NhFhDEVs,st:0</t>
-  </si>
-  <si>
-    <t>http://www.alcoff.com/wp-content/uploads/2023/09/IMG_5824-150x150.jpeg</t>
   </si>
   <si>
     <t>Anita L. Allen</t>
@@ -2853,9 +2841,6 @@
     <t>https://www.youtube.com/watch?v=j4rhY7tmSBg</t>
   </si>
   <si>
-    <t>https://upotv.upo.es/video/5fb232a7abe3c6e3648b45ce</t>
-  </si>
-  <si>
     <t>https://www.paginaindomita.com/susan-moller-okin/</t>
   </si>
   <si>
@@ -3047,9 +3032,6 @@
     <t>https://www.bu.edu/philo/profile/cinzia-arruzza/</t>
   </si>
   <si>
-    <t>https://www.google.com/search?client=opera-gx&amp;q=Cinzia+Arruzza&amp;sourceid=opera&amp;ie=UTF-8&amp;oe=UTF-8#fpstate=ive&amp;vld=cid:4aea1607,vid:9pBqB3M8J9o,st:0</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=GkENhFBGq0M</t>
   </si>
   <si>
@@ -3083,21 +3065,12 @@
     <t>https://www.youtube.com/watch?v=zwx6SkDBku4</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=KR1TguUn1wk</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Lb1ZggsDHvE</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=GaqJ9mgQiYQ</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=vibZTcZzEew</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=Qsk0YZTuir4</t>
-  </si>
-  <si>
     <t>https://cocodriloediciones.com/profile/mariella-sala/</t>
   </si>
   <si>
@@ -3162,9 +3135,6 @@
   </si>
   <si>
     <t>https://alicecrary.com</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Z3s7yRJ_Ceo</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=hpiLrEYffCQ</t>
@@ -3873,9 +3843,6 @@
     <t>https://cef.pucp.edu.pe/wp-content/uploads/2013/02/rosemary_rizopatron-692x1024.jpg</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=WwHF94NosVk</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=ypgh4vPBtG0</t>
   </si>
   <si>
@@ -4062,9 +4029,6 @@
     <t>https://www.fraymocho.com.ar/media/catalog/product/cache/5be8613c49569c873a50ed7e321cb477/9/8/9875745995_9789875745995_2022-11-08_11_12_58.jpg</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=3Dhd4DIhU1A</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=_ws-zxDYdJ8</t>
   </si>
   <si>
@@ -4284,9 +4248,6 @@
     <t xml:space="preserve">Corriente surgida en los años 60-70 que enfatiza la transformación profunda de la sociedad para abolir el patriarcado. Analizan la dominación masculina como un fenómeno estructural y sistémico, no solo como desigualdad en leyes, y consideran que el patriarcado (a saber, el conjunto de normas e instituciones que dan poder a los hombres) es la forma primaria de opresión de las mujeres. </t>
   </si>
   <si>
-    <t>Sistema social y político basado en la primacía de los hombres. En él, la autoridad y los recursos están concentrados en manos masculinas, lo que impone un orden de dominación sobre las mujeres y define «lo propio» de cada género. Como señala Cinzia Arruzza, el término se usa para enfatizar que la opresión de género es un fenómeno constante y estructural, no un hecho aislado. Es decir, bajo el patriarcado la desigualdad de género está arraigada en las instituciones y relaciones sociales, no solo en actitudes personales.</t>
-  </si>
-  <si>
     <t>Teoría política clásica (Rousseau, Hobbes, Locke) que explica el origen del Estado por un pacto voluntario entre individuos. Según esta idea, las personas acuerdan renunciar su libertad natural para constituir un poder común que garantice derechos y deberes. En concreto, el contrato social propone que todos los miembros de la sociedad aceptan reglas y autoridades a cambio de protección y orden.</t>
   </si>
   <si>
@@ -4296,9 +4257,6 @@
     <t>Conjunto de normas y prácticas sociales que asumen la heterosexualidad y la familia nuclear heterosexual como modelo "natural" o normal. En una matriz heteronormativa se presupone que la orientación sexual y la identidad de género deben alinearse (sexo-biológico masculino = identidad masculina, relaciones heterosexuales, roles tradicionales, etc.). Esto invisibiliza y margina otras identidades sexuales y de género, relegándolas como "anormales" en la cultura dominante.</t>
   </si>
   <si>
-    <t>Principio por el cual todas las personas son equiparadas en derechos y obligaciones, sin privilegios o discriminaciones arbitrarias. La RAE la define como el reconocimiento de que todos los ciudadanos tienen el mismo trato jurídico. En la cuestión del género, la igualdad exige que mujeres y hombres disfruten de las mismas oportunidades, derechos y libertades.</t>
-  </si>
-  <si>
     <t>Idea (acepción crítica) de que a las mujeres les corresponde por naturaleza una tarea reproductiva obligatoria, como la maternidad y el cuidado. En el feminismo se rechaza esta "obligación biológica": se argumenta que los roles reproductivos no son meramente inescapables por biología, sino que están influidos por factores sociales y deben ser una elección.</t>
   </si>
   <si>
@@ -4384,6 +4342,81 @@
   </si>
   <si>
     <t>Todas las formas de ser varón que no corresponden al patrón hegemónico. Incluyen masculinidades subordinadas (con rasgos asociados a lo femenino), cómplices (que se benefician de la hegemonía sin liderarla) y otras identidades alternativas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema social y político basado en la primacía de los hombres. En él, la autoridad y los recursos están concentrados en manos masculinas, lo que impone un orden de dominación sobre las mujeres y define «lo propio» de cada género. Como señala Cinzia Arruzza, el término se usa para enfatizar que la opresión de género es un fenómeno constante y estructural (arraigada en las instituciones y relaciones sociales), no un hecho aislado de actitudes personales. </t>
+  </si>
+  <si>
+    <t>Principio por el cual todas las personas son equiparadas en derechos y obligaciones, sin privilegios o discriminaciones arbitrarias. En la cuestión del género, la igualdad exige que mujeres y hombres disfruten de las mismas oportunidades, derechos y libertades.</t>
+  </si>
+  <si>
+    <t>-33.92515116300965</t>
+  </si>
+  <si>
+    <t>151.13498218554994</t>
+  </si>
+  <si>
+    <t>Gender and power (1987), Masculinities (1995), Souther Theory: The Global Dynamics of Knowledge in Social Science (2007)</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1387737466i/3369056.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/4a/Dianne-Reggett.jpg</t>
+  </si>
+  <si>
+    <t>Masculinidades, teoría social, estudios queer</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vIaGthbEjec</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raewyn Connell (1944– )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Socióloga australiana y una de las principales teóricas en los estudios de género y masculinidades. Su obra ha sido fundamental para comprender el género como una estructura de relaciones sociales atravesada por el poder. Es conocida por desarrollar el concepto de masculinidad hegemónica, que explica cómo ciertas formas de masculinidad se imponen como dominantes, subordinando tanto a las mujeres como a otras masculinidades. En textos como Masculinities (1995), Connell muestra que estas jerarquías no son naturales, sino históricas y cambiantes, y que se reproducen en instituciones como la familia, la escuela y el Estado.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://images.pagina12.com.ar/styles/focal_3_2_960x640/public/2023-08/760985-img-9168.jpg?h=e5aec6c8&amp;itok=i_1gagwW</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=g2bmnwehlpA&amp;t=85s</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XyGKkHnxqs8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gU7hK5cuwks</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=M2C3egr83-c</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fz_TrR6K5MQ</t>
+  </si>
+  <si>
+    <t>http://www.raewynconnell.net</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZqwlLHju9vo</t>
   </si>
 </sst>
 </file>
@@ -4451,12 +4484,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -4527,7 +4566,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4611,14 +4650,54 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4947,7 +5026,7 @@
     <col min="6" max="6" width="13.85546875" style="22" customWidth="1"/>
     <col min="7" max="7" width="16.28515625" style="5" customWidth="1"/>
     <col min="8" max="8" width="15" style="5" customWidth="1"/>
-    <col min="9" max="9" width="16" style="5" customWidth="1"/>
+    <col min="9" max="9" width="29.85546875" style="5" customWidth="1"/>
     <col min="10" max="10" width="25.140625" style="23" customWidth="1"/>
     <col min="11" max="11" width="25.5703125" style="21" customWidth="1"/>
     <col min="12" max="12" width="24.28515625" style="21" customWidth="1"/>
@@ -4958,7 +5037,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -5002,10 +5081,10 @@
     </row>
     <row r="2" spans="1:14" ht="21.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>56</v>
@@ -5014,30 +5093,30 @@
         <v>57</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>329</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>333</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5045,7 +5124,7 @@
         <v>28</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>58</v>
@@ -5054,13 +5133,13 @@
         <v>59</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>334</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>338</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
@@ -5068,16 +5147,16 @@
         <v>60</v>
       </c>
       <c r="K3" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>340</v>
-      </c>
       <c r="N3" s="10" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5085,19 +5164,19 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>120</v>
@@ -5114,7 +5193,7 @@
         <v>62</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>116</v>
@@ -5131,13 +5210,13 @@
         <v>71</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="8" t="s">
@@ -5156,7 +5235,7 @@
         <v>121</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="N5" s="10" t="s">
         <v>124</v>
@@ -5167,27 +5246,25 @@
         <v>14</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H6" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I6" s="9"/>
+      <c r="I6" s="34"/>
       <c r="J6" s="6" t="s">
         <v>127</v>
       </c>
@@ -5198,7 +5275,7 @@
         <v>130</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="N6" s="10" t="s">
         <v>129</v>
@@ -5215,35 +5292,35 @@
         <v>69</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="N7" s="14" t="s">
         <v>133</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5257,35 +5334,35 @@
         <v>70</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="M8" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="N8" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5293,41 +5370,41 @@
         <v>50</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J9" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="L9" s="6" t="s">
+      <c r="M9" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>145</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="N9" s="14" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5341,35 +5418,35 @@
         <v>70</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5383,77 +5460,77 @@
         <v>70</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>169</v>
-      </c>
       <c r="J11" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="M11" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="N11" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J12" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="N12" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5467,40 +5544,40 @@
         <v>70</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="J13" s="6" t="s">
+      <c r="L13" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="N13" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B14" s="6">
         <v>1941</v>
@@ -5509,35 +5586,35 @@
         <v>61</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>192</v>
-      </c>
       <c r="K14" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5548,35 +5625,35 @@
         <v>1966</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="N15" s="16" t="s">
         <v>7</v>
@@ -5593,82 +5670,82 @@
         <v>70</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="K16" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="N16" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="J16" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:14" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>70</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="G17" s="34"/>
+      <c r="H17" s="36" t="s">
+        <v>938</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="N17" s="37" t="s">
         <v>170</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B18" s="6">
         <v>1968</v>
@@ -5677,35 +5754,35 @@
         <v>70</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J18" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="N18" s="14" t="s">
         <v>242</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="N18" s="14" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5719,77 +5796,77 @@
         <v>70</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="38" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="13">
         <v>1955</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="E20" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="G20" s="34"/>
+      <c r="H20" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="I20" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>259</v>
+      <c r="J20" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>638</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="N20" s="41" t="s">
+        <v>937</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5803,35 +5880,35 @@
         <v>70</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K21" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="L21" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="L21" s="6" t="s">
-        <v>267</v>
-      </c>
       <c r="M21" s="6" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5839,83 +5916,83 @@
         <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="H22" s="9"/>
       <c r="I22" s="25" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="K22" s="25" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" s="38" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="C23" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>526</v>
-      </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="25" t="s">
-        <v>527</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>634</v>
-      </c>
-      <c r="K23" s="25" t="s">
+      <c r="E23" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>415</v>
+      </c>
+      <c r="G23" s="36" t="s">
+        <v>939</v>
+      </c>
+      <c r="H23" s="34"/>
+      <c r="I23" s="36" t="s">
+        <v>522</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="K23" s="36" t="s">
+        <v>625</v>
+      </c>
+      <c r="L23" s="13" t="s">
         <v>635</v>
       </c>
-      <c r="L23" s="6" t="s">
-        <v>645</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="N23" s="10" t="s">
-        <v>277</v>
+      <c r="M23" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="N23" s="37" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5923,41 +6000,41 @@
         <v>41</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="25" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="K24" s="25" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -5971,35 +6048,35 @@
         <v>70</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="25" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="K25" s="25" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6007,41 +6084,41 @@
         <v>52</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="25" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="K26" s="25" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -6055,35 +6132,35 @@
         <v>70</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="8" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="K27" s="25" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6097,35 +6174,35 @@
         <v>70</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="25" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="K28" s="25" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6142,32 +6219,32 @@
         <v>87</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="G29" s="9"/>
       <c r="H29" s="25" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="K29" s="25" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6178,38 +6255,38 @@
         <v>1957</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>88</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="25" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="K30" s="25" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N30" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6217,41 +6294,41 @@
         <v>36</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>88</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="25" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="K31" s="25" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6268,32 +6345,32 @@
         <v>87</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="25" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="K32" s="25" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="N32" s="10" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6310,32 +6387,32 @@
         <v>73</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="25" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="I33" s="25" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="K33" s="25" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6343,7 +6420,7 @@
         <v>43</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>72</v>
@@ -6352,32 +6429,32 @@
         <v>73</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="25" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="I34" s="25" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="K34" s="25" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="N34" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -6394,32 +6471,32 @@
         <v>83</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="25" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="K35" s="25" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6436,32 +6513,32 @@
         <v>83</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="25" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="I36" s="25" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="K36" s="25" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6469,7 +6546,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>84</v>
@@ -6478,32 +6555,32 @@
         <v>83</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="25" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K37" s="25" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6511,41 +6588,41 @@
         <v>75</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="H38" s="9"/>
       <c r="I38" s="25" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>111</v>
       </c>
       <c r="K38" s="25" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>104</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6559,35 +6636,35 @@
         <v>89</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="25" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I39" s="25" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="K39" s="27" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6601,35 +6678,35 @@
         <v>89</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="25" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="I40" s="25" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="K40" s="27" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6643,35 +6720,35 @@
         <v>89</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I41" s="25" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="K41" s="25" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6685,35 +6762,35 @@
         <v>89</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="G42" s="9"/>
       <c r="H42" s="25" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I42" s="25" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="K42" s="25" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="L42" s="6" t="s">
         <v>107</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N42" s="10" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6727,35 +6804,35 @@
         <v>89</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="G43" s="9"/>
       <c r="H43" s="25" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I43" s="25" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="K43" s="25" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6763,41 +6840,41 @@
         <v>78</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G44" s="9"/>
       <c r="H44" s="25" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I44" s="25" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="K44" s="25" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N44" s="10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6811,77 +6888,77 @@
         <v>89</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="25" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I45" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="K45" s="25" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="B46" s="6">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="B46" s="13">
         <v>1976</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="G46" s="9"/>
-      <c r="H46" s="25" t="s">
-        <v>578</v>
-      </c>
-      <c r="I46" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>737</v>
-      </c>
-      <c r="K46" s="25" t="s">
-        <v>738</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>662</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="N46" s="10" t="s">
-        <v>302</v>
+      <c r="C46" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F46" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="G46" s="34"/>
+      <c r="H46" s="36" t="s">
+        <v>944</v>
+      </c>
+      <c r="I46" s="36" t="s">
+        <v>572</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="K46" s="36" t="s">
+        <v>728</v>
+      </c>
+      <c r="L46" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="M46" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="N46" s="37" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6889,41 +6966,41 @@
         <v>13</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="25" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="K47" s="25" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="L47" s="6" t="s">
         <v>63</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -6931,41 +7008,41 @@
         <v>31</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="G48" s="25" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="25" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="K48" s="25" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="L48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6976,38 +7053,38 @@
         <v>1937</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="G49" s="9"/>
       <c r="H49" s="25" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="I49" s="25" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="K49" s="25" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7015,41 +7092,41 @@
         <v>51</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="H50" s="9"/>
       <c r="I50" s="25" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="K50" s="25" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7063,35 +7140,35 @@
         <v>66</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="H51" s="9"/>
       <c r="I51" s="25" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="K51" s="25" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7105,77 +7182,73 @@
         <v>67</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="G52" s="25" t="s">
-        <v>589</v>
-      </c>
-      <c r="H52" s="25" t="s">
-        <v>590</v>
-      </c>
-      <c r="I52" s="9"/>
+        <v>487</v>
+      </c>
+      <c r="F52" s="35" t="s">
+        <v>488</v>
+      </c>
+      <c r="G52" s="36" t="s">
+        <v>583</v>
+      </c>
+      <c r="H52" s="36"/>
+      <c r="I52" s="34"/>
       <c r="J52" s="6" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="K52" s="25" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" s="38" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="13">
         <v>1943</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="G53" s="25" t="s">
-        <v>592</v>
-      </c>
-      <c r="H53" s="25" t="s">
-        <v>591</v>
-      </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="6" t="s">
-        <v>751</v>
-      </c>
-      <c r="K53" s="25" t="s">
-        <v>752</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>667</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="N53" s="10" t="s">
-        <v>309</v>
+      <c r="D53" s="34" t="s">
+        <v>432</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="F53" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="G53" s="36" t="s">
+        <v>584</v>
+      </c>
+      <c r="H53" s="36"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="13" t="s">
+        <v>741</v>
+      </c>
+      <c r="K53" s="36" t="s">
+        <v>742</v>
+      </c>
+      <c r="L53" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="M53" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="N53" s="37" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7186,38 +7259,36 @@
         <v>1942</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G54" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="H54" s="25" t="s">
-        <v>593</v>
-      </c>
-      <c r="I54" s="9"/>
+        <v>491</v>
+      </c>
+      <c r="F54" s="35" t="s">
+        <v>492</v>
+      </c>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36" t="s">
+        <v>585</v>
+      </c>
+      <c r="I54" s="34"/>
       <c r="J54" s="6" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="K54" s="25" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7231,35 +7302,35 @@
         <v>90</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G55" s="9"/>
       <c r="H55" s="25" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="I55" s="25" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="K55" s="25" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -7267,7 +7338,7 @@
         <v>23</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>85</v>
@@ -7276,74 +7347,74 @@
         <v>85</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G56" s="25" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="H56" s="9"/>
       <c r="I56" s="25" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="13">
         <v>1953</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="25" t="s">
-        <v>600</v>
-      </c>
-      <c r="I57" s="25" t="s">
-        <v>599</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="K57" s="25" t="s">
-        <v>760</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="M57" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>313</v>
+      <c r="E57" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="F57" s="35" t="s">
+        <v>498</v>
+      </c>
+      <c r="G57" s="13"/>
+      <c r="H57" s="36" t="s">
+        <v>591</v>
+      </c>
+      <c r="I57" s="36" t="s">
+        <v>590</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="K57" s="36" t="s">
+        <v>750</v>
+      </c>
+      <c r="L57" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="M57" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="N57" s="37" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7357,35 +7428,35 @@
         <v>86</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G58" s="9"/>
       <c r="H58" s="25" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="I58" s="25" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="K58" s="25" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7402,32 +7473,32 @@
         <v>85</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="G59" s="9"/>
       <c r="H59" s="25" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="I59" s="25" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="K59" s="25" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -7441,35 +7512,35 @@
         <v>95</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="25" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="I60" s="25" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="K60" s="25" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="L60" s="6" t="s">
         <v>96</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7483,35 +7554,35 @@
         <v>95</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G61" s="9"/>
       <c r="H61" s="25" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="I61" s="25" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="K61" s="25" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7528,32 +7599,32 @@
         <v>93</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="G62" s="9"/>
       <c r="H62" s="25" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="I62" s="25" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7570,32 +7641,32 @@
         <v>93</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="G63" s="9"/>
       <c r="H63" s="25" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="I63" s="27" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="K63" s="25" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="L63" s="6" t="s">
         <v>98</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7612,32 +7683,32 @@
         <v>93</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="G64" s="9"/>
       <c r="H64" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I64" s="25" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="K64" s="25" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="L64" s="6" t="s">
         <v>100</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -7654,79 +7725,79 @@
         <v>103</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G65" s="9"/>
       <c r="H65" s="25" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="I65" s="25" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="K65" s="25" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="B66" s="6">
+        <v>192</v>
+      </c>
+      <c r="B66" s="13">
         <v>1967</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="G66" s="9"/>
-      <c r="H66" s="25" t="s">
-        <v>617</v>
-      </c>
-      <c r="I66" s="25" t="s">
-        <v>616</v>
-      </c>
-      <c r="J66" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="K66" s="25" t="s">
-        <v>778</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="M66" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="N66" s="10" t="s">
-        <v>323</v>
+      <c r="D66" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E66" s="35" t="s">
+        <v>515</v>
+      </c>
+      <c r="F66" s="35" t="s">
+        <v>516</v>
+      </c>
+      <c r="G66" s="34"/>
+      <c r="H66" s="36" t="s">
+        <v>941</v>
+      </c>
+      <c r="I66" s="36" t="s">
+        <v>607</v>
+      </c>
+      <c r="J66" s="13" t="s">
+        <v>767</v>
+      </c>
+      <c r="K66" s="36" t="s">
+        <v>768</v>
+      </c>
+      <c r="L66" s="13" t="s">
+        <v>665</v>
+      </c>
+      <c r="M66" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="N66" s="37" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B67" s="6">
         <v>1953</v>
@@ -7735,40 +7806,40 @@
         <v>70</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="G67" s="9"/>
       <c r="H67" s="25" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="I67" s="25" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="K67" s="25" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B68" s="17">
         <v>1976</v>
@@ -7777,40 +7848,40 @@
         <v>70</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G68" s="9"/>
       <c r="H68" s="27" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="I68" s="27" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="K68" s="27" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="L68" s="17" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="M68" s="17" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="N68" s="10" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B69" s="17">
         <v>1925</v>
@@ -7822,228 +7893,232 @@
         <v>103</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="G69" s="9"/>
       <c r="H69" s="27" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="I69" s="27" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="K69" s="27" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="L69" s="17" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="M69" s="17" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="N69" s="27" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D70" s="21" t="s">
         <v>88</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="G70" s="9"/>
       <c r="H70" s="27" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="I70" s="27" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J70" s="23" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="K70" s="27" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="L70" s="21" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="M70" s="21" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="N70" s="27" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>681</v>
-      </c>
-      <c r="C71" s="21" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" s="38" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="38" t="s">
+        <v>671</v>
+      </c>
+      <c r="B71" s="42"/>
+      <c r="C71" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="D71" s="21" t="s">
-        <v>434</v>
-      </c>
-      <c r="E71" s="22" t="s">
-        <v>687</v>
-      </c>
-      <c r="F71" s="22" t="s">
-        <v>688</v>
-      </c>
-      <c r="G71" s="9"/>
-      <c r="H71" s="27" t="s">
-        <v>805</v>
-      </c>
-      <c r="I71" s="9"/>
-      <c r="J71" s="23" t="s">
+      <c r="D71" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="E71" s="43" t="s">
+        <v>677</v>
+      </c>
+      <c r="F71" s="43" t="s">
+        <v>678</v>
+      </c>
+      <c r="G71" s="34"/>
+      <c r="H71" s="41" t="s">
+        <v>942</v>
+      </c>
+      <c r="I71" s="34"/>
+      <c r="J71" s="44" t="s">
+        <v>778</v>
+      </c>
+      <c r="K71" s="41" t="s">
+        <v>781</v>
+      </c>
+      <c r="L71" s="42" t="s">
+        <v>670</v>
+      </c>
+      <c r="M71" s="42" t="s">
         <v>788</v>
       </c>
-      <c r="K71" s="27" t="s">
-        <v>791</v>
-      </c>
-      <c r="L71" s="21" t="s">
-        <v>680</v>
-      </c>
-      <c r="M71" s="21" t="s">
-        <v>798</v>
-      </c>
-      <c r="N71" s="27" t="s">
-        <v>802</v>
+      <c r="N71" s="41" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="C72" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="G72" s="9"/>
       <c r="H72" s="27" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="I72" s="27" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="J72" s="23" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="K72" s="27" t="s">
+        <v>783</v>
+      </c>
+      <c r="L72" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="M72" s="21" t="s">
+        <v>789</v>
+      </c>
+      <c r="N72" s="27" t="s">
         <v>793</v>
-      </c>
-      <c r="L72" s="21" t="s">
-        <v>683</v>
-      </c>
-      <c r="M72" s="21" t="s">
-        <v>799</v>
-      </c>
-      <c r="N72" s="27" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C73" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="G73" s="9"/>
       <c r="H73" s="27" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="I73" s="27" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="J73" s="23" t="s">
+        <v>784</v>
+      </c>
+      <c r="K73" s="27" t="s">
+        <v>785</v>
+      </c>
+      <c r="L73" s="21" t="s">
+        <v>675</v>
+      </c>
+      <c r="M73" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="N73" s="27" t="s">
         <v>794</v>
       </c>
-      <c r="K73" s="27" t="s">
+    </row>
+    <row r="74" spans="1:14" s="38" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="38" t="s">
+        <v>623</v>
+      </c>
+      <c r="B74" s="42"/>
+      <c r="C74" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="D74" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="E74" s="43" t="s">
+        <v>681</v>
+      </c>
+      <c r="F74" s="43" t="s">
+        <v>682</v>
+      </c>
+      <c r="G74" s="34"/>
+      <c r="H74" s="45" t="s">
+        <v>800</v>
+      </c>
+      <c r="I74" s="41" t="s">
+        <v>800</v>
+      </c>
+      <c r="J74" s="44" t="s">
+        <v>787</v>
+      </c>
+      <c r="K74" s="41" t="s">
+        <v>786</v>
+      </c>
+      <c r="L74" s="42" t="s">
+        <v>676</v>
+      </c>
+      <c r="M74" s="42" t="s">
+        <v>791</v>
+      </c>
+      <c r="N74" s="41" t="s">
         <v>795</v>
-      </c>
-      <c r="L73" s="21" t="s">
-        <v>685</v>
-      </c>
-      <c r="M73" s="21" t="s">
-        <v>800</v>
-      </c>
-      <c r="N73" s="27" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="C74" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>434</v>
-      </c>
-      <c r="E74" s="22" t="s">
-        <v>691</v>
-      </c>
-      <c r="F74" s="22" t="s">
-        <v>692</v>
-      </c>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="27" t="s">
-        <v>810</v>
-      </c>
-      <c r="J74" s="23" t="s">
-        <v>797</v>
-      </c>
-      <c r="K74" s="27" t="s">
-        <v>796</v>
-      </c>
-      <c r="L74" s="21" t="s">
-        <v>686</v>
-      </c>
-      <c r="M74" s="21" t="s">
-        <v>801</v>
-      </c>
-      <c r="N74" s="27" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B75" s="21">
         <v>1947</v>
@@ -8052,77 +8127,75 @@
         <v>90</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>434</v>
-      </c>
-      <c r="E75" s="22" t="s">
-        <v>817</v>
-      </c>
-      <c r="F75" s="22" t="s">
-        <v>818</v>
-      </c>
-      <c r="G75" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="E75" s="43" t="s">
+        <v>806</v>
+      </c>
+      <c r="F75" s="43" t="s">
+        <v>807</v>
+      </c>
+      <c r="G75" s="36"/>
+      <c r="H75" s="41" t="s">
+        <v>802</v>
+      </c>
+      <c r="I75" s="34"/>
+      <c r="J75" s="44" t="s">
+        <v>779</v>
+      </c>
+      <c r="K75" s="27" t="s">
+        <v>780</v>
+      </c>
+      <c r="L75" s="21" t="s">
+        <v>813</v>
+      </c>
+      <c r="M75" s="21" t="s">
         <v>812</v>
       </c>
-      <c r="H75" s="27" t="s">
-        <v>813</v>
-      </c>
-      <c r="I75" s="9"/>
-      <c r="J75" s="23" t="s">
-        <v>789</v>
-      </c>
-      <c r="K75" s="27" t="s">
-        <v>790</v>
-      </c>
-      <c r="L75" s="21" t="s">
-        <v>824</v>
-      </c>
-      <c r="M75" s="21" t="s">
-        <v>823</v>
-      </c>
       <c r="N75" s="27" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
     </row>
     <row r="76" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>814</v>
+        <v>803</v>
       </c>
       <c r="C76" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>434</v>
-      </c>
-      <c r="E76" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="E76" s="43" t="s">
+        <v>804</v>
+      </c>
+      <c r="F76" s="43" t="s">
+        <v>805</v>
+      </c>
+      <c r="G76" s="34"/>
+      <c r="H76" s="41" t="s">
+        <v>810</v>
+      </c>
+      <c r="I76" s="34"/>
+      <c r="J76" s="44" t="s">
+        <v>809</v>
+      </c>
+      <c r="K76" s="27" t="s">
+        <v>811</v>
+      </c>
+      <c r="L76" s="21" t="s">
         <v>815</v>
       </c>
-      <c r="F76" s="22" t="s">
-        <v>816</v>
-      </c>
-      <c r="G76" s="9"/>
-      <c r="H76" s="27" t="s">
-        <v>821</v>
-      </c>
-      <c r="I76" s="9"/>
-      <c r="J76" s="23" t="s">
-        <v>820</v>
-      </c>
-      <c r="K76" s="27" t="s">
-        <v>822</v>
-      </c>
-      <c r="L76" s="21" t="s">
-        <v>826</v>
-      </c>
       <c r="M76" s="21" t="s">
-        <v>825</v>
+        <v>814</v>
       </c>
       <c r="N76" s="27" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="B77" s="21">
         <v>1965</v>
@@ -8131,165 +8204,199 @@
         <v>85</v>
       </c>
       <c r="D77" s="21" t="s">
+        <v>817</v>
+      </c>
+      <c r="E77" s="43" t="s">
+        <v>830</v>
+      </c>
+      <c r="F77" s="43" t="s">
+        <v>831</v>
+      </c>
+      <c r="G77" s="41" t="s">
+        <v>829</v>
+      </c>
+      <c r="H77" s="41"/>
+      <c r="I77" s="34"/>
+      <c r="J77" s="44" t="s">
+        <v>827</v>
+      </c>
+      <c r="K77" s="27" t="s">
         <v>828</v>
       </c>
-      <c r="E77" s="22" t="s">
-        <v>842</v>
-      </c>
-      <c r="F77" s="22" t="s">
-        <v>843</v>
-      </c>
-      <c r="G77" s="27" t="s">
-        <v>841</v>
-      </c>
-      <c r="H77" s="27" t="s">
-        <v>840</v>
-      </c>
-      <c r="I77" s="9"/>
-      <c r="J77" s="23" t="s">
-        <v>838</v>
-      </c>
-      <c r="K77" s="27" t="s">
-        <v>839</v>
-      </c>
       <c r="L77" s="21" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="M77" s="21" t="s">
-        <v>827</v>
+        <v>816</v>
       </c>
       <c r="N77" s="27" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>831</v>
+        <v>820</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>836</v>
+        <v>825</v>
       </c>
       <c r="D78" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="E78" s="22" t="s">
+      <c r="E78" s="43" t="s">
+        <v>832</v>
+      </c>
+      <c r="F78" s="43" t="s">
+        <v>833</v>
+      </c>
+      <c r="G78" s="36" t="s">
         <v>844</v>
       </c>
-      <c r="F78" s="22" t="s">
-        <v>845</v>
-      </c>
-      <c r="G78" s="25" t="s">
+      <c r="H78" s="34"/>
+      <c r="I78" s="34"/>
+      <c r="J78" s="44" t="s">
         <v>856</v>
       </c>
-      <c r="H78" s="9"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="23" t="s">
-        <v>868</v>
-      </c>
       <c r="K78" s="27" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="L78" s="21" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="M78" s="21" t="s">
-        <v>830</v>
+        <v>819</v>
       </c>
       <c r="N78" s="27" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
     </row>
     <row r="79" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="C79" s="21" t="s">
         <v>70</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="E79" s="22" t="s">
-        <v>846</v>
-      </c>
-      <c r="F79" s="22" t="s">
-        <v>847</v>
-      </c>
-      <c r="G79" s="25" t="s">
-        <v>849</v>
-      </c>
-      <c r="H79" s="9"/>
-      <c r="I79" s="27" t="s">
-        <v>853</v>
-      </c>
-      <c r="J79" s="23" t="s">
-        <v>851</v>
+        <v>157</v>
+      </c>
+      <c r="E79" s="43" t="s">
+        <v>834</v>
+      </c>
+      <c r="F79" s="43" t="s">
+        <v>835</v>
+      </c>
+      <c r="G79" s="36" t="s">
+        <v>837</v>
+      </c>
+      <c r="H79" s="34"/>
+      <c r="I79" s="41" t="s">
+        <v>841</v>
+      </c>
+      <c r="J79" s="44" t="s">
+        <v>839</v>
       </c>
       <c r="K79" s="27" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="L79" s="21" t="s">
-        <v>835</v>
+        <v>824</v>
       </c>
       <c r="M79" s="21" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="N79" s="27" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
     </row>
     <row r="80" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="C80" s="21" t="s">
         <v>70</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="F80" s="22" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="G80" s="25" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="H80" s="9"/>
       <c r="I80" s="9"/>
       <c r="J80" s="23" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="K80" s="27" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="L80" s="21" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="M80" s="21" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="N80" s="27" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="38" t="s">
+        <v>901</v>
+      </c>
+      <c r="B81" s="21">
+        <v>1944</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" s="22" t="s">
+        <v>929</v>
+      </c>
+      <c r="F81" s="22" t="s">
+        <v>930</v>
+      </c>
+      <c r="H81" s="27" t="s">
+        <v>935</v>
+      </c>
+      <c r="I81" s="39" t="s">
+        <v>943</v>
+      </c>
+      <c r="J81" s="23" t="s">
+        <v>931</v>
+      </c>
+      <c r="K81" s="27" t="s">
+        <v>932</v>
+      </c>
+      <c r="L81" s="21" t="s">
+        <v>934</v>
+      </c>
+      <c r="M81" s="21" t="s">
+        <v>936</v>
+      </c>
+      <c r="N81" s="27" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E87" s="24"/>
     </row>
   </sheetData>
@@ -8305,307 +8412,306 @@
     <hyperlink ref="K6" r:id="rId9" xr:uid="{D53DE5AD-EE79-46F3-A856-319913D5AC4F}"/>
     <hyperlink ref="N6" r:id="rId10" xr:uid="{DDA12806-89D6-428F-AFFE-6C65C42D723B}"/>
     <hyperlink ref="H6" r:id="rId11" xr:uid="{5002C16A-6320-4682-8C87-ED15EE9492C7}"/>
-    <hyperlink ref="G6" r:id="rId12" xr:uid="{2E447AD7-BD5E-4E8A-B4D8-F2F5090A08AC}"/>
-    <hyperlink ref="N7" r:id="rId13" xr:uid="{07875741-8F53-4E98-9B30-DA069128FFC9}"/>
-    <hyperlink ref="K7" r:id="rId14" xr:uid="{C0AF8490-0577-48E4-A9FD-ED7BD8C7ECA9}"/>
-    <hyperlink ref="I7" r:id="rId15" xr:uid="{FE02FB33-C794-46FA-9705-FEA5DBCA2508}"/>
-    <hyperlink ref="H7" r:id="rId16" xr:uid="{D0E617CC-AD1A-4B9F-BF8B-B3C0AF23AE2E}"/>
-    <hyperlink ref="N8" r:id="rId17" xr:uid="{C1CD3FAA-CD4E-4C40-BBCD-EAEC177ACB3B}"/>
-    <hyperlink ref="K8" r:id="rId18" xr:uid="{3088EAAE-69F4-4794-BDEA-CC30C907E1CE}"/>
-    <hyperlink ref="H8" r:id="rId19" xr:uid="{BBF9F461-33B1-4F37-8EE8-5C9A452445CA}"/>
-    <hyperlink ref="G8" r:id="rId20" xr:uid="{EB64DA36-E2C5-4749-97CD-1B40B4CF457E}"/>
-    <hyperlink ref="N9" r:id="rId21" xr:uid="{A399F9E1-7175-4780-A9E4-281C2DF0D40F}"/>
-    <hyperlink ref="K9" r:id="rId22" xr:uid="{CEC3F048-C1DC-4813-9391-673747DB8A99}"/>
-    <hyperlink ref="H21" r:id="rId23" xr:uid="{EB91A356-2977-46EB-B3A9-B66E293E846E}"/>
-    <hyperlink ref="H11" r:id="rId24" xr:uid="{66F7834B-F54E-4970-A1D4-630E0809AE06}"/>
-    <hyperlink ref="H19" r:id="rId25" xr:uid="{F5F56B87-ECC8-4FE8-A555-54F31183F78F}"/>
-    <hyperlink ref="H17" r:id="rId26" xr:uid="{59288067-B7C2-45B9-ADDC-626CB445D924}"/>
-    <hyperlink ref="I9" r:id="rId27" xr:uid="{0B2F7C70-5F3A-4F9F-A006-601A85054648}"/>
-    <hyperlink ref="G9" r:id="rId28" xr:uid="{BDF28F0D-CB02-4078-8412-29B8578A1EA3}"/>
-    <hyperlink ref="N10" r:id="rId29" xr:uid="{401EA379-D878-4C14-AC11-0C275C4F41CB}"/>
-    <hyperlink ref="K10" r:id="rId30" xr:uid="{E497107B-3622-4CA8-B4E5-F594CEF9B1C5}"/>
-    <hyperlink ref="I10" r:id="rId31" xr:uid="{C398A044-F72A-4BD1-9329-BB31257F547E}"/>
-    <hyperlink ref="G10" r:id="rId32" xr:uid="{C81003C1-C3F2-4F67-8C97-D20BFFADC658}"/>
-    <hyperlink ref="K11" r:id="rId33" xr:uid="{2F1198C2-7189-4EEC-BC5C-3D489A62380D}"/>
-    <hyperlink ref="N11" r:id="rId34" xr:uid="{BD8C6950-356F-4BA0-AF9D-AFD8DD4DF485}"/>
-    <hyperlink ref="I15" r:id="rId35" xr:uid="{BF888950-57DB-47B3-B071-79F7B6173B20}"/>
-    <hyperlink ref="I11" r:id="rId36" xr:uid="{4DE3CA9D-FA60-4781-B5A7-80B333573BAD}"/>
-    <hyperlink ref="I17" r:id="rId37" xr:uid="{EB85DA83-6111-4432-97AD-39A2CF04AC8F}"/>
-    <hyperlink ref="N17" r:id="rId38" xr:uid="{A5E0573E-7EAC-40DF-9652-579E59120545}"/>
-    <hyperlink ref="K17" r:id="rId39" xr:uid="{01C4B63E-535C-43A4-96B7-81FF40AEC41C}"/>
-    <hyperlink ref="K12" r:id="rId40" xr:uid="{78B1E9FC-5345-4D91-A181-01EAA6B3812C}"/>
-    <hyperlink ref="N12" r:id="rId41" xr:uid="{A6CDFF5B-1B95-44C6-BEE2-7B0E7224434D}"/>
-    <hyperlink ref="H12" r:id="rId42" xr:uid="{0E95D209-CC81-4126-9DBE-520331B80C7F}"/>
-    <hyperlink ref="I12" r:id="rId43" xr:uid="{C1516D60-E896-42DB-B1C7-7F8DE471D73D}"/>
-    <hyperlink ref="I13" r:id="rId44" xr:uid="{C04AAA3C-C4F5-4431-B593-85F36B1E387E}"/>
-    <hyperlink ref="H13" r:id="rId45" xr:uid="{20A317EF-D6F0-4455-9FD8-EB14742DEFD4}"/>
-    <hyperlink ref="K13" r:id="rId46" xr:uid="{B8417BAD-BC27-4D2C-A013-5EB93F62FDC1}"/>
-    <hyperlink ref="N13" r:id="rId47" xr:uid="{06D99598-AB96-4593-8B63-F024E9F5BEDD}"/>
-    <hyperlink ref="H14" r:id="rId48" xr:uid="{0C6FA3AB-ABF4-4025-B6CD-B4A8AE75EEE6}"/>
-    <hyperlink ref="N14" r:id="rId49" xr:uid="{6904A400-BE0F-449D-A003-697884FFC8DB}"/>
-    <hyperlink ref="K14" r:id="rId50" xr:uid="{FA3A01AA-BB5B-4BA5-92B3-7B1294FA7C99}"/>
-    <hyperlink ref="I14" r:id="rId51" xr:uid="{0227A9ED-B549-428A-85B1-D95A09C53DA3}"/>
-    <hyperlink ref="K15" r:id="rId52" xr:uid="{3B781866-3004-48B8-AE63-6A4541D5CACE}"/>
-    <hyperlink ref="H15" r:id="rId53" xr:uid="{980FDCF3-A359-4427-BC18-E0C4FC549745}"/>
-    <hyperlink ref="I16" r:id="rId54" xr:uid="{E9CA00EF-7E43-4FC4-8E21-3B88AE031370}"/>
-    <hyperlink ref="H16" r:id="rId55" xr:uid="{32D57982-71C5-4809-A4C1-554210320B91}"/>
-    <hyperlink ref="N16" r:id="rId56" xr:uid="{11B295F8-F906-48A4-ACAE-6B26BC80E8BD}"/>
-    <hyperlink ref="K16" r:id="rId57" xr:uid="{95419884-516C-40F0-85F6-B577B68F0906}"/>
-    <hyperlink ref="I18" r:id="rId58" xr:uid="{F3446782-E68E-42C7-A784-85C5131A4B9C}"/>
-    <hyperlink ref="K18" r:id="rId59" xr:uid="{D40939DB-CE9B-44EC-9A8F-B33EDC823229}"/>
-    <hyperlink ref="N18" r:id="rId60" xr:uid="{66E5A4AB-0FB2-4C86-AF3A-342106809142}"/>
-    <hyperlink ref="H18" r:id="rId61" xr:uid="{66C9EB80-E6E2-4BE3-AC91-37B342E5DD57}"/>
-    <hyperlink ref="K19" r:id="rId62" xr:uid="{1075522C-DC66-42A0-A192-D7AAFB349A1F}"/>
-    <hyperlink ref="N19" r:id="rId63" xr:uid="{BAD72FDF-02B8-43A9-99E1-C96EFFBA8C85}"/>
-    <hyperlink ref="K20" r:id="rId64" xr:uid="{C9247626-AE69-41F5-B799-81FD7C2A7634}"/>
-    <hyperlink ref="I19" r:id="rId65" xr:uid="{8F73E293-1DEC-459D-B346-C7C6AA722329}"/>
-    <hyperlink ref="I20" r:id="rId66" xr:uid="{7655620E-5884-4A0B-936A-6FB0C53DB1A8}"/>
-    <hyperlink ref="H20" r:id="rId67" location="fpstate=ive&amp;vld=cid:59edc99d,vid:6y2NhFhDEVs,st:0" display="https://www.google.com/search?q=linda+martin+Alcoff+entrevista&amp;client=opera-gx&amp;hs=r5g&amp;sca_esv=e0a8504cdddaab2b&amp;biw=1324&amp;bih=611&amp;sxsrf=ANbL-n53WnxGOPJ37GWsJ12i1lc4WwDzyw%3A1773545143598&amp;ei=tya2afOaJMnY1sQP-qPK0AY&amp;ved=0ahUKEwiz0pvC-qCTAxVJrJUCHfqREmoQ4dUDCBM&amp;uact=5&amp;oq=linda+martin+Alcoff+entrevista&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiHmxpbmRhIG1hcnRpbiBBbGNvZmYgZW50cmV2aXN0YTIFECEYoAEyBRAhGKABMgUQIRigAUiXC1DIAlilCnABeACQAQCYAXmgAdEHqgEDOC4yuAEDyAEA-AEBmAIKoAKRB8ICCxAAGIAEGLADGKIEwgIIEAAYsAMY7wWYAwCIBgGQBgSSBwM3LjOgB-0ZsgcDNi4zuAeOB8IHBDAuMTDIBw6ACAA&amp;sclient=gws-wiz-serp#fpstate=ive&amp;vld=cid:59edc99d,vid:6y2NhFhDEVs,st:0" xr:uid="{9333523F-0F48-43D8-B2B0-554EFA6E93FE}"/>
-    <hyperlink ref="N20" r:id="rId68" xr:uid="{DB9F8705-1837-4BD4-B67C-E4F4BDE7D6E8}"/>
-    <hyperlink ref="K21" r:id="rId69" xr:uid="{03C4AE30-7BF2-4D8E-89F8-0A83822D914C}"/>
-    <hyperlink ref="I21" r:id="rId70" xr:uid="{1DC1558A-2AC2-40C0-871F-2A3C232910A0}"/>
-    <hyperlink ref="N21" r:id="rId71" xr:uid="{C11C5D4C-A957-4525-A092-7BD92A71C9D8}"/>
-    <hyperlink ref="N24" r:id="rId72" xr:uid="{BF0E0748-626E-4B99-90F5-7F0AE13811D1}"/>
-    <hyperlink ref="N22" r:id="rId73" xr:uid="{2F5349C8-2EED-4F43-A4C8-930D7A8A10E1}"/>
-    <hyperlink ref="N23" r:id="rId74" xr:uid="{3B9D629B-0768-4217-83AB-43A32CBAACB2}"/>
-    <hyperlink ref="N25" r:id="rId75" xr:uid="{504CB9DA-76AD-4B3A-AA8F-731363566742}"/>
-    <hyperlink ref="N26" r:id="rId76" xr:uid="{C532889E-DA51-4533-AD4F-AD19426BD329}"/>
-    <hyperlink ref="I27" r:id="rId77" xr:uid="{1B44DD4E-CE6B-403E-95CB-58A2680AB649}"/>
-    <hyperlink ref="N27" r:id="rId78" xr:uid="{21F2B7A5-429E-49CA-8165-164C4678D73C}"/>
-    <hyperlink ref="N28" r:id="rId79" xr:uid="{3545DA37-18BA-459D-A314-145D459A6F41}"/>
-    <hyperlink ref="N29" r:id="rId80" xr:uid="{E8EFA1DF-0D27-46DC-89C9-C45095330F87}"/>
-    <hyperlink ref="N30" r:id="rId81" xr:uid="{9911B323-9CE8-4269-AC5D-768540B9BA5C}"/>
-    <hyperlink ref="N31" r:id="rId82" xr:uid="{41CF60B2-D65A-4297-AE0C-3103538B4A9F}"/>
-    <hyperlink ref="N32" r:id="rId83" xr:uid="{5DC7D0A7-08ED-4FE2-80FA-21DAE2915BAA}"/>
-    <hyperlink ref="N33" r:id="rId84" xr:uid="{C194BB97-32FA-453A-B456-3CC49ABEEED9}"/>
-    <hyperlink ref="N34" r:id="rId85" xr:uid="{0DABB3AC-3934-4008-BD59-0531523763A1}"/>
-    <hyperlink ref="I35" r:id="rId86" xr:uid="{61AFEB1E-4D3E-4FFC-B87D-8F1D28C15E94}"/>
-    <hyperlink ref="N35" r:id="rId87" xr:uid="{49D24060-2A16-42FF-A223-A6F14D3AD842}"/>
-    <hyperlink ref="N36" r:id="rId88" xr:uid="{63A169E4-4D08-4D4A-A084-FCD4998D10B9}"/>
-    <hyperlink ref="N37" r:id="rId89" xr:uid="{D3D13E50-8F7B-4B5D-B096-B0D6E269E4AD}"/>
-    <hyperlink ref="N38" r:id="rId90" xr:uid="{ADB1DA12-3C63-47E8-99A1-BAA3C634EF5C}"/>
-    <hyperlink ref="N39" r:id="rId91" xr:uid="{EAAE9A45-F4FA-4450-A0B2-FE1D371B4B35}"/>
-    <hyperlink ref="N40" r:id="rId92" xr:uid="{DA97380A-08DE-446B-B5FD-B6019E7C8A1D}"/>
-    <hyperlink ref="H41" r:id="rId93" xr:uid="{F82E1B42-DA55-41D6-9315-67BF456201ED}"/>
-    <hyperlink ref="N41" r:id="rId94" xr:uid="{4A2A28AA-24FD-4EBB-B3E8-10E85824F1E6}"/>
-    <hyperlink ref="N42" r:id="rId95" xr:uid="{C4454BB2-131E-4EBA-BE9C-922F98C15E80}"/>
-    <hyperlink ref="N43" r:id="rId96" xr:uid="{28D48277-BEF6-41C8-9A21-B96A8F5EF9D9}"/>
-    <hyperlink ref="N44" r:id="rId97" xr:uid="{C0426974-553C-4E8C-9C17-42626FCE2DB8}"/>
-    <hyperlink ref="N45" r:id="rId98" xr:uid="{1C972A44-84A5-4B19-9C82-06A67B71F419}"/>
-    <hyperlink ref="N46" r:id="rId99" xr:uid="{00C868F3-F6B7-4D1F-B842-067E675D6B3B}"/>
-    <hyperlink ref="N47" r:id="rId100" xr:uid="{9463CF82-74E5-428A-8F97-2EEA7C577006}"/>
-    <hyperlink ref="N48" r:id="rId101" xr:uid="{42E02085-E92F-4A78-9245-A30ED14A189A}"/>
-    <hyperlink ref="N49" r:id="rId102" xr:uid="{D9317F17-1503-48A4-AC48-DE103C50DC42}"/>
-    <hyperlink ref="N50" r:id="rId103" xr:uid="{2197E6BB-4E13-4E23-A262-1329F68DAD55}"/>
-    <hyperlink ref="N51" r:id="rId104" xr:uid="{BD08F022-1421-4B24-9B9E-CCA7A768B495}"/>
-    <hyperlink ref="N52" r:id="rId105" xr:uid="{CFEC6FE8-5F77-4796-97DE-7015ED300FDD}"/>
-    <hyperlink ref="N53" r:id="rId106" xr:uid="{CAB66B0E-C0F3-4C2F-A3FE-EFEFFF4D5980}"/>
-    <hyperlink ref="N54" r:id="rId107" xr:uid="{809F2C9B-36A7-4A70-AE18-2CC711B47B3C}"/>
-    <hyperlink ref="N55" r:id="rId108" xr:uid="{9E7CFAB3-AA31-4F66-8A8B-39A624DDBBA1}"/>
-    <hyperlink ref="N56" r:id="rId109" xr:uid="{23335A61-0220-45B5-81C3-48D3E34D04F6}"/>
-    <hyperlink ref="N57" r:id="rId110" xr:uid="{688424D4-7A09-4C7E-A5CC-E2A0567F0CF2}"/>
-    <hyperlink ref="N58" r:id="rId111" xr:uid="{90920865-BDEE-4571-9783-81F896010EDD}"/>
-    <hyperlink ref="N59" r:id="rId112" xr:uid="{01193DD4-34F7-49FE-977E-C13AF637445A}"/>
-    <hyperlink ref="N60" r:id="rId113" xr:uid="{A5340B9F-7777-4533-88B4-4C8E6C20A59E}"/>
-    <hyperlink ref="N61" r:id="rId114" xr:uid="{C3104B5D-5FF0-4516-B4B1-F95AB4F02AB7}"/>
-    <hyperlink ref="N62" r:id="rId115" xr:uid="{45E19747-4179-4E0D-A64A-6A93C5EED941}"/>
-    <hyperlink ref="N63" r:id="rId116" xr:uid="{625E13E7-21A9-4E55-BC30-440C7956256C}"/>
-    <hyperlink ref="N64" r:id="rId117" xr:uid="{53B5DCB4-3F97-4844-9D02-4AA5E2808177}"/>
-    <hyperlink ref="H64" r:id="rId118" xr:uid="{593FF400-26BC-41F0-B0D8-2099350B3034}"/>
-    <hyperlink ref="N65" r:id="rId119" xr:uid="{EA10CA29-573D-4327-B913-80616E4E5C74}"/>
-    <hyperlink ref="N66" r:id="rId120" xr:uid="{E372022C-82F2-4091-8F34-5A0069BF8D66}"/>
-    <hyperlink ref="N67" r:id="rId121" xr:uid="{558BBA40-081A-470A-92CE-4E23EA8AE9FF}"/>
-    <hyperlink ref="N68" r:id="rId122" xr:uid="{E5B6BF4B-3912-421F-BF30-3419AD928941}"/>
-    <hyperlink ref="N3" r:id="rId123" xr:uid="{37FC5E07-A54B-4135-B647-D8FAF04CDA02}"/>
-    <hyperlink ref="N2" r:id="rId124" xr:uid="{04E82C90-C991-472D-BF86-CCBBE78EE66D}"/>
-    <hyperlink ref="K2" r:id="rId125" xr:uid="{3807BE86-3A7F-4819-A74A-D8390A60A763}"/>
-    <hyperlink ref="G2" r:id="rId126" xr:uid="{7677D849-306F-4D84-B84E-7F34557BDCBD}"/>
-    <hyperlink ref="K3" r:id="rId127" xr:uid="{29450970-39DB-41B7-8010-75E800C3C8D4}"/>
-    <hyperlink ref="G3" r:id="rId128" xr:uid="{9D420FF6-4BBC-45CD-9927-70CB8B794430}"/>
-    <hyperlink ref="G22" r:id="rId129" xr:uid="{A08BBCCE-BD3A-4A78-8821-51B45070A37B}"/>
-    <hyperlink ref="G23" r:id="rId130" xr:uid="{483E5F20-7464-4538-BD04-03094D1E1AFD}"/>
-    <hyperlink ref="I23" r:id="rId131" xr:uid="{D7FF6B2D-638B-44BC-A45A-1D77702E83B0}"/>
-    <hyperlink ref="I22" r:id="rId132" xr:uid="{AB66B096-620B-4CE9-84B0-09AD5A11A798}"/>
-    <hyperlink ref="H24" r:id="rId133" xr:uid="{9ACE5488-AC37-452A-B9DB-AF9822654C3B}"/>
-    <hyperlink ref="I24" r:id="rId134" xr:uid="{42C8AF0B-279C-4881-9CF9-B8824D5BFBE8}"/>
-    <hyperlink ref="I25" r:id="rId135" xr:uid="{124B8AFE-29BB-448D-AD51-7729A6A92274}"/>
-    <hyperlink ref="G25" r:id="rId136" xr:uid="{D8D34155-7AF1-425D-94DB-9AD4A3D89FDE}"/>
-    <hyperlink ref="I26" r:id="rId137" xr:uid="{A6348DEE-52E6-439B-BF57-6AA9EB73165D}"/>
-    <hyperlink ref="G26" r:id="rId138" xr:uid="{3F56D024-33C5-407F-B594-4208C7C7CA3D}"/>
-    <hyperlink ref="G27" r:id="rId139" xr:uid="{79DD6B19-2210-4758-B339-F0F9933E7260}"/>
-    <hyperlink ref="H28" r:id="rId140" xr:uid="{9937956B-5115-49F0-B517-189F0CCEBC17}"/>
-    <hyperlink ref="H29" r:id="rId141" xr:uid="{9731DD3C-5BDB-49D1-8CE9-AB54980A8A41}"/>
-    <hyperlink ref="I29" r:id="rId142" xr:uid="{7FE2B3CA-E871-45CB-9D91-09E4E3BD2209}"/>
-    <hyperlink ref="H30" r:id="rId143" xr:uid="{B7D25D40-411E-41B4-978E-10C02CE68A0C}"/>
-    <hyperlink ref="I30" r:id="rId144" xr:uid="{0006B7F0-0FF8-48F4-87C7-B151538243AB}"/>
-    <hyperlink ref="H31" r:id="rId145" xr:uid="{A414CE39-FE1F-4289-B69F-38562E6D6904}"/>
-    <hyperlink ref="I31" r:id="rId146" xr:uid="{38ABB0A4-B872-4837-BF79-B4A63B08D9E0}"/>
-    <hyperlink ref="G32" r:id="rId147" xr:uid="{53312060-D111-4214-8544-BAE3505ADC13}"/>
-    <hyperlink ref="I32" r:id="rId148" xr:uid="{070946D8-0494-4439-925B-9965292938DB}"/>
-    <hyperlink ref="I33" r:id="rId149" xr:uid="{B7265443-833F-4E5D-8A3C-0E5640CFA14E}"/>
-    <hyperlink ref="H33" r:id="rId150" xr:uid="{3A93D353-E7D6-4B99-9F81-0B95FEBBF0CE}"/>
-    <hyperlink ref="I34" r:id="rId151" xr:uid="{562C0C97-98EA-48A6-A448-3659B7F43F6F}"/>
-    <hyperlink ref="H34" r:id="rId152" xr:uid="{7F29F009-C4B2-4160-B36E-55FE9C8DE108}"/>
-    <hyperlink ref="H35" r:id="rId153" xr:uid="{3B106540-C553-4822-BBD8-A80BBA6F8A67}"/>
-    <hyperlink ref="I36" r:id="rId154" xr:uid="{44BDAC26-3D9A-40A2-BF0B-A04D153876CF}"/>
-    <hyperlink ref="H36" r:id="rId155" xr:uid="{237F2EEA-4710-4223-82AE-70C3B6CF7AF0}"/>
-    <hyperlink ref="I37" r:id="rId156" xr:uid="{52550C92-47F1-4EF2-A1B9-E08DF54F8C75}"/>
-    <hyperlink ref="G37" r:id="rId157" xr:uid="{CFAEA637-199F-4BD8-B4DF-1D3FFEB2042A}"/>
-    <hyperlink ref="G38" r:id="rId158" xr:uid="{9A89CEC6-F4F4-49CA-943E-360F33D9C05F}"/>
-    <hyperlink ref="I38" r:id="rId159" xr:uid="{792C3B0E-A4E6-406E-96DB-F1099A72C0EF}"/>
-    <hyperlink ref="H39" r:id="rId160" xr:uid="{4920519A-420B-4C1D-9137-ABF5BF36A758}"/>
-    <hyperlink ref="I39" r:id="rId161" xr:uid="{C91CDC38-7F7C-447B-ABDA-D4EEE352EA12}"/>
-    <hyperlink ref="H40" r:id="rId162" xr:uid="{36486386-FDBB-434B-A92A-733C3891480F}"/>
-    <hyperlink ref="I40" r:id="rId163" xr:uid="{82E8640D-8F71-413D-B44B-6D328021A04A}"/>
-    <hyperlink ref="I41" r:id="rId164" xr:uid="{73080944-A3BF-4160-B555-FDB4223EBF02}"/>
-    <hyperlink ref="H42" r:id="rId165" xr:uid="{360A7008-FA04-416D-847F-77C7743D087D}"/>
-    <hyperlink ref="I42" r:id="rId166" xr:uid="{9685B4C7-737F-4376-B12F-51770912B002}"/>
-    <hyperlink ref="I43" r:id="rId167" xr:uid="{42A51A8B-430D-4882-BB92-7BB32B9EC3B4}"/>
-    <hyperlink ref="H43" r:id="rId168" xr:uid="{268827F1-F1D2-48E0-985F-98F536A13A86}"/>
-    <hyperlink ref="I44" r:id="rId169" xr:uid="{3BD89FAD-2317-4479-84E5-9D08000ABCC1}"/>
-    <hyperlink ref="H44" r:id="rId170" xr:uid="{BD54F60C-3658-466D-BFB8-F30DBE913FEB}"/>
-    <hyperlink ref="H45" r:id="rId171" xr:uid="{8EA7A96E-44D0-4F2D-89DD-4B59436BF805}"/>
-    <hyperlink ref="I45" r:id="rId172" xr:uid="{6C3DB6FA-C741-437B-ACE4-2645ECA0A0A2}"/>
-    <hyperlink ref="I46" r:id="rId173" xr:uid="{8A73320E-C545-4454-A0A7-FE6849DF947F}"/>
-    <hyperlink ref="H46" r:id="rId174" location="fpstate=ive&amp;vld=cid:4aea1607,vid:9pBqB3M8J9o,st:0" xr:uid="{FF792A0E-A603-41EE-9B12-D0F26E0AE950}"/>
-    <hyperlink ref="G47" r:id="rId175" xr:uid="{F69D80EA-3D6C-43B2-A639-A1B07EEFAD1E}"/>
-    <hyperlink ref="I47" r:id="rId176" xr:uid="{2FBF0E0E-082E-4392-8703-D9FFE03F48DB}"/>
-    <hyperlink ref="I48" r:id="rId177" xr:uid="{BE3C0C6B-3F9B-4C3B-B761-DEB35643F7C7}"/>
-    <hyperlink ref="G48" r:id="rId178" xr:uid="{75E10BFD-2507-4A0A-9BD0-C1A3CBF7EE57}"/>
-    <hyperlink ref="I49" r:id="rId179" xr:uid="{DE1FFF05-3CCB-45BE-8F2E-9209EB6C29C0}"/>
-    <hyperlink ref="H49" r:id="rId180" xr:uid="{9A4D3D1B-01AB-450A-A4C9-5D8AD5D13473}"/>
-    <hyperlink ref="I50" r:id="rId181" xr:uid="{1D67BFC3-184F-4FE9-926F-394FC48E85BF}"/>
-    <hyperlink ref="G50" r:id="rId182" xr:uid="{BB0F5B9F-8548-4CA1-BB41-95BA0E09C752}"/>
-    <hyperlink ref="G51" r:id="rId183" xr:uid="{7C329507-3CD8-47DC-9D6C-02ED91780B57}"/>
-    <hyperlink ref="I51" r:id="rId184" xr:uid="{DE8D4BEA-0C5E-494F-9CDF-35E89386A6F6}"/>
-    <hyperlink ref="G52" r:id="rId185" xr:uid="{0CC903E1-5E41-4111-9DAD-B1490CA2F312}"/>
-    <hyperlink ref="H52" r:id="rId186" xr:uid="{9AAF510B-51D8-47F4-A20E-7DF0BCD6A15E}"/>
-    <hyperlink ref="H53" r:id="rId187" xr:uid="{16E3CA7A-4747-41F5-AD70-FEAA908218CF}"/>
-    <hyperlink ref="G53" r:id="rId188" xr:uid="{284ACA6D-6A22-492C-B7A3-3ADC419EFA1C}"/>
-    <hyperlink ref="H54" r:id="rId189" xr:uid="{5255DADE-DE2B-4D49-9E7B-474AF74AAC3F}"/>
-    <hyperlink ref="G54" r:id="rId190" xr:uid="{A849F83D-8FA0-49BC-9C65-29DBDB5C9365}"/>
-    <hyperlink ref="I55" r:id="rId191" xr:uid="{C785577A-2620-4B77-9326-1935205B6C6B}"/>
-    <hyperlink ref="H55" r:id="rId192" xr:uid="{9433CCDD-A447-49C8-A52D-9DF561FB5B79}"/>
-    <hyperlink ref="G56" r:id="rId193" xr:uid="{8B887C99-ED41-49FF-ADDF-108A37698023}"/>
-    <hyperlink ref="I56" r:id="rId194" xr:uid="{27C0E075-5E01-41D3-9831-7C026E208139}"/>
-    <hyperlink ref="I57" r:id="rId195" xr:uid="{A473A945-4AEA-4961-934E-F8FDF96A5CF0}"/>
-    <hyperlink ref="H57" r:id="rId196" xr:uid="{8F6CCB07-D35D-4931-8CA6-D1C6D9221B09}"/>
-    <hyperlink ref="H58" r:id="rId197" xr:uid="{6D9D43A8-F3E8-4FCA-AE98-CA178F5EF340}"/>
-    <hyperlink ref="I58" r:id="rId198" xr:uid="{0318FE14-789B-4A30-B628-488D0EF62717}"/>
-    <hyperlink ref="I59" r:id="rId199" xr:uid="{12ACD367-7913-4B5A-B979-6B2C13045C32}"/>
-    <hyperlink ref="H59" r:id="rId200" xr:uid="{89363B48-32EB-4FD9-AD42-3B008DC16ECC}"/>
-    <hyperlink ref="H60" r:id="rId201" xr:uid="{44BA83E7-6B2D-45FB-9E1B-ABA9462CE72A}"/>
-    <hyperlink ref="I60" r:id="rId202" xr:uid="{52A628CA-BEE8-4884-8DFA-72FFAB628F1D}"/>
-    <hyperlink ref="I61" r:id="rId203" xr:uid="{3CA6545D-67F7-4752-A37D-C8649EB1519B}"/>
-    <hyperlink ref="H61" r:id="rId204" xr:uid="{C5CAC2EE-FF96-4DB6-A0FD-603330DD048F}"/>
-    <hyperlink ref="I62" r:id="rId205" xr:uid="{EB7A3412-8E2E-45EE-B264-1BDA24FA00DC}"/>
-    <hyperlink ref="H62" r:id="rId206" xr:uid="{102CCCCE-E36B-4608-A2ED-6A88461EAD32}"/>
-    <hyperlink ref="H63" r:id="rId207" xr:uid="{DEB0983B-C46B-40D7-98A5-A601516F030C}"/>
-    <hyperlink ref="I63" r:id="rId208" xr:uid="{A7018CFA-A172-4A58-B62F-D2667DB0FAAA}"/>
-    <hyperlink ref="I64" r:id="rId209" xr:uid="{FF37EB8E-9B82-4E91-A623-B19DFADE9691}"/>
-    <hyperlink ref="H65" r:id="rId210" xr:uid="{43F705D0-9A65-4F78-ADD5-EF43D2B115ED}"/>
-    <hyperlink ref="I65" r:id="rId211" xr:uid="{67DDF291-6115-411E-90F3-5FCA82C46D07}"/>
-    <hyperlink ref="I66" r:id="rId212" xr:uid="{AFAFFE97-C4A0-4A53-96BC-221B0E0EB495}"/>
-    <hyperlink ref="H66" r:id="rId213" xr:uid="{71A36470-339C-45F0-97C4-59870BAB1800}"/>
-    <hyperlink ref="H67" r:id="rId214" xr:uid="{B542E46F-74CA-486D-AB6B-49E22E7E33AD}"/>
-    <hyperlink ref="I67" r:id="rId215" xr:uid="{5F70A2B5-417A-49FF-88A4-45F73948DC0E}"/>
-    <hyperlink ref="H68" r:id="rId216" xr:uid="{B6477C3E-0C0B-4EE4-A3FF-0F779251F9D6}"/>
-    <hyperlink ref="I68" r:id="rId217" xr:uid="{969AEE4F-87B0-407E-B833-BABBA3FE527C}"/>
-    <hyperlink ref="H69" r:id="rId218" xr:uid="{0EC72919-0858-4041-BD31-274AB257F00D}"/>
-    <hyperlink ref="I69" r:id="rId219" xr:uid="{AF42E53D-0F60-4143-B6F1-735309478748}"/>
-    <hyperlink ref="H70" r:id="rId220" xr:uid="{D994144C-7AA8-4F87-BCE3-703642981B3D}"/>
-    <hyperlink ref="I70" r:id="rId221" xr:uid="{012A9EFE-C117-45AA-BB30-685F1A261071}"/>
-    <hyperlink ref="N70" r:id="rId222" xr:uid="{774D77B5-0430-4076-9713-0BB7CB346BE7}"/>
-    <hyperlink ref="N69" r:id="rId223" xr:uid="{E09D5140-A745-45CE-B33A-B371B8C64607}"/>
-    <hyperlink ref="K22" r:id="rId224" xr:uid="{92D679AA-AC98-44ED-A5F0-F224927E9356}"/>
-    <hyperlink ref="K23" r:id="rId225" xr:uid="{E9F62591-8EE9-4998-92DA-31EBDBC44853}"/>
-    <hyperlink ref="K24" r:id="rId226" xr:uid="{C1A074D4-2F5F-4801-84C7-DB2B113C54DE}"/>
-    <hyperlink ref="K25" r:id="rId227" xr:uid="{24CBF6B9-E57E-4219-A1AF-B551EB068C3B}"/>
-    <hyperlink ref="K26" r:id="rId228" xr:uid="{4E0A9F61-9239-4156-9D6E-9A6C2BCF6362}"/>
-    <hyperlink ref="K27" r:id="rId229" xr:uid="{7DDD7074-25B0-48F5-B03C-B2DD143C9A14}"/>
-    <hyperlink ref="K28" r:id="rId230" xr:uid="{CBAD55B0-AF3E-4EC3-A376-ABD55BD9A744}"/>
-    <hyperlink ref="K29" r:id="rId231" xr:uid="{06147B81-0B2B-41B6-955F-223540232648}"/>
-    <hyperlink ref="K30" r:id="rId232" xr:uid="{A7DBE007-A1B3-4A11-8208-34F3956B6684}"/>
-    <hyperlink ref="K31" r:id="rId233" xr:uid="{DB16E36B-384A-45A4-8108-6167DF4D58D2}"/>
-    <hyperlink ref="K32" r:id="rId234" xr:uid="{7773509F-194D-434E-9815-9B9CD96F1B4A}"/>
-    <hyperlink ref="K33" r:id="rId235" xr:uid="{C4C82EE3-575F-4D87-AABE-D2B09FB81FA6}"/>
-    <hyperlink ref="K34" r:id="rId236" xr:uid="{B7BA3F8A-06F4-46E3-A6C5-DF7482F62FB2}"/>
-    <hyperlink ref="K35" r:id="rId237" xr:uid="{4268C150-1693-4BE8-8613-BA55D16ED91B}"/>
-    <hyperlink ref="K36" r:id="rId238" xr:uid="{640326C2-C7BE-4D0F-BAC5-B92897FD31ED}"/>
-    <hyperlink ref="K37" r:id="rId239" xr:uid="{AF354A09-E5E7-4880-B34F-053B60677E71}"/>
-    <hyperlink ref="K38" r:id="rId240" xr:uid="{D0A42DA3-B6C4-47C5-9AF3-07D7D84ED81C}"/>
-    <hyperlink ref="K39" r:id="rId241" xr:uid="{7B943E8D-D35C-4AEE-8D30-A284C8F20C01}"/>
-    <hyperlink ref="K40" r:id="rId242" xr:uid="{EBE20291-EE62-49AC-9129-C6F2934B943F}"/>
-    <hyperlink ref="K41" r:id="rId243" xr:uid="{C1FF2774-9DFA-4244-B748-AF9AE16F3F84}"/>
-    <hyperlink ref="K42" r:id="rId244" xr:uid="{832ACE54-5C2A-418D-8885-DDF7FE0F253A}"/>
-    <hyperlink ref="K43" r:id="rId245" xr:uid="{57E3972A-68F8-4B3B-B114-BD972770F69C}"/>
-    <hyperlink ref="K44" r:id="rId246" xr:uid="{3955EBC1-FEF0-4AF3-964F-108D07765E6C}"/>
-    <hyperlink ref="K45" r:id="rId247" xr:uid="{B6539D79-ABA4-46BA-91D8-9EF6A2CDD129}"/>
-    <hyperlink ref="K46" r:id="rId248" xr:uid="{A2053E3D-6A9A-469F-903D-32D383D0FFAF}"/>
-    <hyperlink ref="K47" r:id="rId249" xr:uid="{56F5CF9C-F452-400A-BD14-B91D4D039032}"/>
-    <hyperlink ref="K48" r:id="rId250" xr:uid="{A9B36DFF-C234-48BF-B5E5-40E91EE84062}"/>
-    <hyperlink ref="K49" r:id="rId251" xr:uid="{94744859-1786-4833-9501-7D8C92D7AACC}"/>
-    <hyperlink ref="K50" r:id="rId252" xr:uid="{721A79C2-6C7E-4C1C-A283-E2C6523CF464}"/>
-    <hyperlink ref="K51" r:id="rId253" xr:uid="{3155EFF4-85FB-4171-82F3-F4FEF14E8F3C}"/>
-    <hyperlink ref="K52" r:id="rId254" xr:uid="{88739B09-EFBF-4415-AEF0-0A2F4EC05E66}"/>
-    <hyperlink ref="K53" r:id="rId255" xr:uid="{67D52B33-95C2-4585-A046-0C6F9B0B8D5B}"/>
-    <hyperlink ref="K54" r:id="rId256" xr:uid="{6AC0C8D4-4727-4BC9-9ED9-DCC8F548F82B}"/>
-    <hyperlink ref="K55" r:id="rId257" xr:uid="{C1D85E40-83E2-48BD-ABD3-E19251AFA2E2}"/>
-    <hyperlink ref="K56" r:id="rId258" xr:uid="{4FE3D899-817D-42D5-84EC-7FA4B94D10FF}"/>
-    <hyperlink ref="K57" r:id="rId259" xr:uid="{6A81878E-6BED-4415-8B2E-311785BBBA3C}"/>
-    <hyperlink ref="K58" r:id="rId260" xr:uid="{F6CE14BA-880C-455B-B447-BCBCF0220BCF}"/>
-    <hyperlink ref="K59" r:id="rId261" xr:uid="{A2A5637F-D312-49D2-8258-5795462AE4DE}"/>
-    <hyperlink ref="K60" r:id="rId262" xr:uid="{F4DA95F7-4F6D-4398-841E-C515F8EEB1E4}"/>
-    <hyperlink ref="K61" r:id="rId263" xr:uid="{ACAA867E-D445-4528-B5D2-02BA6A6F1779}"/>
-    <hyperlink ref="K62" r:id="rId264" xr:uid="{94631832-2396-4F59-A9C8-3AC80F5A167B}"/>
-    <hyperlink ref="K63" r:id="rId265" xr:uid="{00FE511F-767B-4392-B69D-D8413969EE3C}"/>
-    <hyperlink ref="K64" r:id="rId266" xr:uid="{0B4C561E-33C5-4A52-871E-F4F4DEDF73AC}"/>
-    <hyperlink ref="K65" r:id="rId267" xr:uid="{5AAF75E4-3DA5-4D86-8DAE-C6ECD44F2390}"/>
-    <hyperlink ref="K66" r:id="rId268" xr:uid="{F0BBE0AD-88AA-4284-85B5-B8668C71F53C}"/>
-    <hyperlink ref="K67" r:id="rId269" xr:uid="{EDF52BEC-A677-4BDA-BE78-EF693942CE38}"/>
-    <hyperlink ref="K68" r:id="rId270" xr:uid="{F71807C8-D7EC-4830-B41C-F58DFE8ADFE3}"/>
-    <hyperlink ref="K69" r:id="rId271" xr:uid="{D9481A01-E888-44B9-A550-B25FD0C40144}"/>
-    <hyperlink ref="K70" r:id="rId272" xr:uid="{48501ED3-8A1F-46A6-AF34-EA1086A21E9E}"/>
-    <hyperlink ref="K75" r:id="rId273" xr:uid="{A616A30C-336A-441E-AEA8-AA6A45A372CC}"/>
-    <hyperlink ref="K71" r:id="rId274" xr:uid="{F392E331-605B-4657-BD9F-B92B4FC52DF2}"/>
-    <hyperlink ref="K72" r:id="rId275" xr:uid="{E87EAE23-E8B5-46EE-8506-078EDC4ECE18}"/>
-    <hyperlink ref="K73" r:id="rId276" xr:uid="{EC336D72-89F6-41E5-8D45-559B001CD3C5}"/>
-    <hyperlink ref="K74" r:id="rId277" xr:uid="{3EBC7866-56B5-45E7-AB20-C579CADD97B9}"/>
-    <hyperlink ref="N71" r:id="rId278" xr:uid="{C287E580-B43F-4161-AEEE-04FD434E8001}"/>
-    <hyperlink ref="N72" r:id="rId279" xr:uid="{8AC448D2-E0F2-48CE-A37E-3DCFE279C06B}"/>
-    <hyperlink ref="N73" r:id="rId280" xr:uid="{AD2FD7FC-9B1B-4C96-8E6A-031D76E5CC9B}"/>
-    <hyperlink ref="N74" r:id="rId281" xr:uid="{0CC50197-D061-4F15-BCEE-7D6B573344AD}"/>
-    <hyperlink ref="H71" r:id="rId282" xr:uid="{1FB76FBF-2338-4060-8E55-16BB79A419A2}"/>
-    <hyperlink ref="H72" r:id="rId283" xr:uid="{CD9A450D-0019-4A6D-95A9-F720BCFF88C5}"/>
-    <hyperlink ref="I72" r:id="rId284" xr:uid="{3FFA0B44-F641-47D6-B287-5BE3CA6C5AB5}"/>
-    <hyperlink ref="I73" r:id="rId285" xr:uid="{F093AA87-D916-4BB2-A320-8EFA680376A4}"/>
-    <hyperlink ref="H73" r:id="rId286" xr:uid="{5F6284C0-96CC-4477-9087-191AA35E2902}"/>
-    <hyperlink ref="I74" r:id="rId287" xr:uid="{9D47BD05-3F5C-4E13-8A2F-A665282E584B}"/>
-    <hyperlink ref="N75" r:id="rId288" xr:uid="{EBD5380E-DB80-4BF6-A61E-A6309E93235F}"/>
-    <hyperlink ref="G75" r:id="rId289" xr:uid="{24169A88-7709-423B-BAF2-89850FC42318}"/>
-    <hyperlink ref="H75" r:id="rId290" xr:uid="{E433EC64-4484-4CBF-8E20-D04AC76381E6}"/>
-    <hyperlink ref="N76" r:id="rId291" xr:uid="{9BB80CDF-1F45-4D34-B964-732422A85FA1}"/>
-    <hyperlink ref="H76" r:id="rId292" xr:uid="{8AE9BF4A-ADDA-4003-A9EC-FF03F3FD45A6}"/>
-    <hyperlink ref="K76" r:id="rId293" xr:uid="{38147578-3C56-41DE-A433-6C76966FDFB5}"/>
-    <hyperlink ref="N77" r:id="rId294" xr:uid="{CB63072D-008E-41FC-B36A-9E78F25CD01B}"/>
-    <hyperlink ref="K77" r:id="rId295" xr:uid="{B800310B-1B67-4F88-97E8-A365C5550B80}"/>
-    <hyperlink ref="H77" r:id="rId296" xr:uid="{22312E91-975C-4786-83A0-6525AB012E2A}"/>
-    <hyperlink ref="G77" r:id="rId297" xr:uid="{849C2ED3-ABCA-4199-BD76-F2AA46588337}"/>
-    <hyperlink ref="N78" r:id="rId298" xr:uid="{BF91105E-213D-493B-8DC6-5D25FC41317E}"/>
-    <hyperlink ref="G79" r:id="rId299" xr:uid="{5641DEA3-15F1-4209-8713-65610EDDB9DC}"/>
-    <hyperlink ref="N79" r:id="rId300" xr:uid="{52D13C80-AB6F-4E9D-AFE3-9898D895534A}"/>
-    <hyperlink ref="K79" r:id="rId301" xr:uid="{00DFBABA-EB23-4041-907B-3FC94D925FB5}"/>
-    <hyperlink ref="I79" r:id="rId302" xr:uid="{0779BC2F-DA16-4077-BF98-E185BA09732E}"/>
-    <hyperlink ref="G78" r:id="rId303" xr:uid="{032C2BC7-0200-485A-9D2D-FD7AF2EA2CAE}"/>
-    <hyperlink ref="K80" r:id="rId304" xr:uid="{00A3006D-6ACD-4C6B-A933-44D9086C0EDC}"/>
-    <hyperlink ref="G80" r:id="rId305" xr:uid="{0E83526C-5F05-4E74-A7C4-93345DE5F738}"/>
-    <hyperlink ref="N80" r:id="rId306" xr:uid="{25F31BFD-BF9A-487F-BDDC-2B60C7AC82CB}"/>
-    <hyperlink ref="K78" r:id="rId307" xr:uid="{A9AF548A-4521-4D15-A568-5A93F4674F41}"/>
+    <hyperlink ref="N7" r:id="rId12" xr:uid="{07875741-8F53-4E98-9B30-DA069128FFC9}"/>
+    <hyperlink ref="K7" r:id="rId13" xr:uid="{C0AF8490-0577-48E4-A9FD-ED7BD8C7ECA9}"/>
+    <hyperlink ref="I7" r:id="rId14" xr:uid="{FE02FB33-C794-46FA-9705-FEA5DBCA2508}"/>
+    <hyperlink ref="H7" r:id="rId15" xr:uid="{D0E617CC-AD1A-4B9F-BF8B-B3C0AF23AE2E}"/>
+    <hyperlink ref="N8" r:id="rId16" xr:uid="{C1CD3FAA-CD4E-4C40-BBCD-EAEC177ACB3B}"/>
+    <hyperlink ref="K8" r:id="rId17" xr:uid="{3088EAAE-69F4-4794-BDEA-CC30C907E1CE}"/>
+    <hyperlink ref="H8" r:id="rId18" xr:uid="{BBF9F461-33B1-4F37-8EE8-5C9A452445CA}"/>
+    <hyperlink ref="G8" r:id="rId19" xr:uid="{EB64DA36-E2C5-4749-97CD-1B40B4CF457E}"/>
+    <hyperlink ref="N9" r:id="rId20" xr:uid="{A399F9E1-7175-4780-A9E4-281C2DF0D40F}"/>
+    <hyperlink ref="K9" r:id="rId21" xr:uid="{CEC3F048-C1DC-4813-9391-673747DB8A99}"/>
+    <hyperlink ref="H21" r:id="rId22" xr:uid="{EB91A356-2977-46EB-B3A9-B66E293E846E}"/>
+    <hyperlink ref="H11" r:id="rId23" xr:uid="{66F7834B-F54E-4970-A1D4-630E0809AE06}"/>
+    <hyperlink ref="H19" r:id="rId24" xr:uid="{F5F56B87-ECC8-4FE8-A555-54F31183F78F}"/>
+    <hyperlink ref="H17" r:id="rId25" xr:uid="{59288067-B7C2-45B9-ADDC-626CB445D924}"/>
+    <hyperlink ref="I9" r:id="rId26" xr:uid="{0B2F7C70-5F3A-4F9F-A006-601A85054648}"/>
+    <hyperlink ref="G9" r:id="rId27" xr:uid="{BDF28F0D-CB02-4078-8412-29B8578A1EA3}"/>
+    <hyperlink ref="N10" r:id="rId28" xr:uid="{401EA379-D878-4C14-AC11-0C275C4F41CB}"/>
+    <hyperlink ref="K10" r:id="rId29" xr:uid="{E497107B-3622-4CA8-B4E5-F594CEF9B1C5}"/>
+    <hyperlink ref="I10" r:id="rId30" xr:uid="{C398A044-F72A-4BD1-9329-BB31257F547E}"/>
+    <hyperlink ref="G10" r:id="rId31" xr:uid="{C81003C1-C3F2-4F67-8C97-D20BFFADC658}"/>
+    <hyperlink ref="K11" r:id="rId32" xr:uid="{2F1198C2-7189-4EEC-BC5C-3D489A62380D}"/>
+    <hyperlink ref="N11" r:id="rId33" xr:uid="{BD8C6950-356F-4BA0-AF9D-AFD8DD4DF485}"/>
+    <hyperlink ref="I15" r:id="rId34" xr:uid="{BF888950-57DB-47B3-B071-79F7B6173B20}"/>
+    <hyperlink ref="I11" r:id="rId35" xr:uid="{4DE3CA9D-FA60-4781-B5A7-80B333573BAD}"/>
+    <hyperlink ref="I17" r:id="rId36" xr:uid="{EB85DA83-6111-4432-97AD-39A2CF04AC8F}"/>
+    <hyperlink ref="N17" r:id="rId37" xr:uid="{A5E0573E-7EAC-40DF-9652-579E59120545}"/>
+    <hyperlink ref="K17" r:id="rId38" xr:uid="{01C4B63E-535C-43A4-96B7-81FF40AEC41C}"/>
+    <hyperlink ref="K12" r:id="rId39" xr:uid="{78B1E9FC-5345-4D91-A181-01EAA6B3812C}"/>
+    <hyperlink ref="N12" r:id="rId40" xr:uid="{A6CDFF5B-1B95-44C6-BEE2-7B0E7224434D}"/>
+    <hyperlink ref="H12" r:id="rId41" xr:uid="{0E95D209-CC81-4126-9DBE-520331B80C7F}"/>
+    <hyperlink ref="I12" r:id="rId42" xr:uid="{C1516D60-E896-42DB-B1C7-7F8DE471D73D}"/>
+    <hyperlink ref="I13" r:id="rId43" xr:uid="{C04AAA3C-C4F5-4431-B593-85F36B1E387E}"/>
+    <hyperlink ref="H13" r:id="rId44" xr:uid="{20A317EF-D6F0-4455-9FD8-EB14742DEFD4}"/>
+    <hyperlink ref="K13" r:id="rId45" xr:uid="{B8417BAD-BC27-4D2C-A013-5EB93F62FDC1}"/>
+    <hyperlink ref="N13" r:id="rId46" xr:uid="{06D99598-AB96-4593-8B63-F024E9F5BEDD}"/>
+    <hyperlink ref="H14" r:id="rId47" xr:uid="{0C6FA3AB-ABF4-4025-B6CD-B4A8AE75EEE6}"/>
+    <hyperlink ref="N14" r:id="rId48" xr:uid="{6904A400-BE0F-449D-A003-697884FFC8DB}"/>
+    <hyperlink ref="K14" r:id="rId49" xr:uid="{FA3A01AA-BB5B-4BA5-92B3-7B1294FA7C99}"/>
+    <hyperlink ref="I14" r:id="rId50" xr:uid="{0227A9ED-B549-428A-85B1-D95A09C53DA3}"/>
+    <hyperlink ref="K15" r:id="rId51" xr:uid="{3B781866-3004-48B8-AE63-6A4541D5CACE}"/>
+    <hyperlink ref="H15" r:id="rId52" xr:uid="{980FDCF3-A359-4427-BC18-E0C4FC549745}"/>
+    <hyperlink ref="I16" r:id="rId53" xr:uid="{E9CA00EF-7E43-4FC4-8E21-3B88AE031370}"/>
+    <hyperlink ref="H16" r:id="rId54" xr:uid="{32D57982-71C5-4809-A4C1-554210320B91}"/>
+    <hyperlink ref="N16" r:id="rId55" xr:uid="{11B295F8-F906-48A4-ACAE-6B26BC80E8BD}"/>
+    <hyperlink ref="K16" r:id="rId56" xr:uid="{95419884-516C-40F0-85F6-B577B68F0906}"/>
+    <hyperlink ref="I18" r:id="rId57" xr:uid="{F3446782-E68E-42C7-A784-85C5131A4B9C}"/>
+    <hyperlink ref="K18" r:id="rId58" xr:uid="{D40939DB-CE9B-44EC-9A8F-B33EDC823229}"/>
+    <hyperlink ref="N18" r:id="rId59" xr:uid="{66E5A4AB-0FB2-4C86-AF3A-342106809142}"/>
+    <hyperlink ref="H18" r:id="rId60" xr:uid="{66C9EB80-E6E2-4BE3-AC91-37B342E5DD57}"/>
+    <hyperlink ref="K19" r:id="rId61" xr:uid="{1075522C-DC66-42A0-A192-D7AAFB349A1F}"/>
+    <hyperlink ref="N19" r:id="rId62" xr:uid="{BAD72FDF-02B8-43A9-99E1-C96EFFBA8C85}"/>
+    <hyperlink ref="K20" r:id="rId63" xr:uid="{C9247626-AE69-41F5-B799-81FD7C2A7634}"/>
+    <hyperlink ref="I19" r:id="rId64" xr:uid="{8F73E293-1DEC-459D-B346-C7C6AA722329}"/>
+    <hyperlink ref="I20" r:id="rId65" xr:uid="{7655620E-5884-4A0B-936A-6FB0C53DB1A8}"/>
+    <hyperlink ref="N20" r:id="rId66" xr:uid="{DB9F8705-1837-4BD4-B67C-E4F4BDE7D6E8}"/>
+    <hyperlink ref="K21" r:id="rId67" xr:uid="{03C4AE30-7BF2-4D8E-89F8-0A83822D914C}"/>
+    <hyperlink ref="I21" r:id="rId68" xr:uid="{1DC1558A-2AC2-40C0-871F-2A3C232910A0}"/>
+    <hyperlink ref="N21" r:id="rId69" xr:uid="{C11C5D4C-A957-4525-A092-7BD92A71C9D8}"/>
+    <hyperlink ref="N24" r:id="rId70" xr:uid="{BF0E0748-626E-4B99-90F5-7F0AE13811D1}"/>
+    <hyperlink ref="N22" r:id="rId71" xr:uid="{2F5349C8-2EED-4F43-A4C8-930D7A8A10E1}"/>
+    <hyperlink ref="N23" r:id="rId72" xr:uid="{3B9D629B-0768-4217-83AB-43A32CBAACB2}"/>
+    <hyperlink ref="N25" r:id="rId73" xr:uid="{504CB9DA-76AD-4B3A-AA8F-731363566742}"/>
+    <hyperlink ref="N26" r:id="rId74" xr:uid="{C532889E-DA51-4533-AD4F-AD19426BD329}"/>
+    <hyperlink ref="I27" r:id="rId75" xr:uid="{1B44DD4E-CE6B-403E-95CB-58A2680AB649}"/>
+    <hyperlink ref="N27" r:id="rId76" xr:uid="{21F2B7A5-429E-49CA-8165-164C4678D73C}"/>
+    <hyperlink ref="N28" r:id="rId77" xr:uid="{3545DA37-18BA-459D-A314-145D459A6F41}"/>
+    <hyperlink ref="N29" r:id="rId78" xr:uid="{E8EFA1DF-0D27-46DC-89C9-C45095330F87}"/>
+    <hyperlink ref="N30" r:id="rId79" xr:uid="{9911B323-9CE8-4269-AC5D-768540B9BA5C}"/>
+    <hyperlink ref="N31" r:id="rId80" xr:uid="{41CF60B2-D65A-4297-AE0C-3103538B4A9F}"/>
+    <hyperlink ref="N32" r:id="rId81" xr:uid="{5DC7D0A7-08ED-4FE2-80FA-21DAE2915BAA}"/>
+    <hyperlink ref="N33" r:id="rId82" xr:uid="{C194BB97-32FA-453A-B456-3CC49ABEEED9}"/>
+    <hyperlink ref="N34" r:id="rId83" xr:uid="{0DABB3AC-3934-4008-BD59-0531523763A1}"/>
+    <hyperlink ref="I35" r:id="rId84" xr:uid="{61AFEB1E-4D3E-4FFC-B87D-8F1D28C15E94}"/>
+    <hyperlink ref="N35" r:id="rId85" xr:uid="{49D24060-2A16-42FF-A223-A6F14D3AD842}"/>
+    <hyperlink ref="N36" r:id="rId86" xr:uid="{63A169E4-4D08-4D4A-A084-FCD4998D10B9}"/>
+    <hyperlink ref="N37" r:id="rId87" xr:uid="{D3D13E50-8F7B-4B5D-B096-B0D6E269E4AD}"/>
+    <hyperlink ref="N38" r:id="rId88" xr:uid="{ADB1DA12-3C63-47E8-99A1-BAA3C634EF5C}"/>
+    <hyperlink ref="N39" r:id="rId89" xr:uid="{EAAE9A45-F4FA-4450-A0B2-FE1D371B4B35}"/>
+    <hyperlink ref="N40" r:id="rId90" xr:uid="{DA97380A-08DE-446B-B5FD-B6019E7C8A1D}"/>
+    <hyperlink ref="H41" r:id="rId91" xr:uid="{F82E1B42-DA55-41D6-9315-67BF456201ED}"/>
+    <hyperlink ref="N41" r:id="rId92" xr:uid="{4A2A28AA-24FD-4EBB-B3E8-10E85824F1E6}"/>
+    <hyperlink ref="N42" r:id="rId93" xr:uid="{C4454BB2-131E-4EBA-BE9C-922F98C15E80}"/>
+    <hyperlink ref="N43" r:id="rId94" xr:uid="{28D48277-BEF6-41C8-9A21-B96A8F5EF9D9}"/>
+    <hyperlink ref="N44" r:id="rId95" xr:uid="{C0426974-553C-4E8C-9C17-42626FCE2DB8}"/>
+    <hyperlink ref="N45" r:id="rId96" xr:uid="{1C972A44-84A5-4B19-9C82-06A67B71F419}"/>
+    <hyperlink ref="N46" r:id="rId97" xr:uid="{00C868F3-F6B7-4D1F-B842-067E675D6B3B}"/>
+    <hyperlink ref="N47" r:id="rId98" xr:uid="{9463CF82-74E5-428A-8F97-2EEA7C577006}"/>
+    <hyperlink ref="N48" r:id="rId99" xr:uid="{42E02085-E92F-4A78-9245-A30ED14A189A}"/>
+    <hyperlink ref="N49" r:id="rId100" xr:uid="{D9317F17-1503-48A4-AC48-DE103C50DC42}"/>
+    <hyperlink ref="N50" r:id="rId101" xr:uid="{2197E6BB-4E13-4E23-A262-1329F68DAD55}"/>
+    <hyperlink ref="N51" r:id="rId102" xr:uid="{BD08F022-1421-4B24-9B9E-CCA7A768B495}"/>
+    <hyperlink ref="N52" r:id="rId103" xr:uid="{CFEC6FE8-5F77-4796-97DE-7015ED300FDD}"/>
+    <hyperlink ref="N53" r:id="rId104" xr:uid="{CAB66B0E-C0F3-4C2F-A3FE-EFEFFF4D5980}"/>
+    <hyperlink ref="N54" r:id="rId105" xr:uid="{809F2C9B-36A7-4A70-AE18-2CC711B47B3C}"/>
+    <hyperlink ref="N55" r:id="rId106" xr:uid="{9E7CFAB3-AA31-4F66-8A8B-39A624DDBBA1}"/>
+    <hyperlink ref="N56" r:id="rId107" xr:uid="{23335A61-0220-45B5-81C3-48D3E34D04F6}"/>
+    <hyperlink ref="N57" r:id="rId108" xr:uid="{688424D4-7A09-4C7E-A5CC-E2A0567F0CF2}"/>
+    <hyperlink ref="N58" r:id="rId109" xr:uid="{90920865-BDEE-4571-9783-81F896010EDD}"/>
+    <hyperlink ref="N59" r:id="rId110" xr:uid="{01193DD4-34F7-49FE-977E-C13AF637445A}"/>
+    <hyperlink ref="N60" r:id="rId111" xr:uid="{A5340B9F-7777-4533-88B4-4C8E6C20A59E}"/>
+    <hyperlink ref="N61" r:id="rId112" xr:uid="{C3104B5D-5FF0-4516-B4B1-F95AB4F02AB7}"/>
+    <hyperlink ref="N62" r:id="rId113" xr:uid="{45E19747-4179-4E0D-A64A-6A93C5EED941}"/>
+    <hyperlink ref="N63" r:id="rId114" xr:uid="{625E13E7-21A9-4E55-BC30-440C7956256C}"/>
+    <hyperlink ref="N64" r:id="rId115" xr:uid="{53B5DCB4-3F97-4844-9D02-4AA5E2808177}"/>
+    <hyperlink ref="H64" r:id="rId116" xr:uid="{593FF400-26BC-41F0-B0D8-2099350B3034}"/>
+    <hyperlink ref="N65" r:id="rId117" xr:uid="{EA10CA29-573D-4327-B913-80616E4E5C74}"/>
+    <hyperlink ref="N66" r:id="rId118" xr:uid="{E372022C-82F2-4091-8F34-5A0069BF8D66}"/>
+    <hyperlink ref="N67" r:id="rId119" xr:uid="{558BBA40-081A-470A-92CE-4E23EA8AE9FF}"/>
+    <hyperlink ref="N68" r:id="rId120" xr:uid="{E5B6BF4B-3912-421F-BF30-3419AD928941}"/>
+    <hyperlink ref="N3" r:id="rId121" xr:uid="{37FC5E07-A54B-4135-B647-D8FAF04CDA02}"/>
+    <hyperlink ref="N2" r:id="rId122" xr:uid="{04E82C90-C991-472D-BF86-CCBBE78EE66D}"/>
+    <hyperlink ref="K2" r:id="rId123" xr:uid="{3807BE86-3A7F-4819-A74A-D8390A60A763}"/>
+    <hyperlink ref="G2" r:id="rId124" xr:uid="{7677D849-306F-4D84-B84E-7F34557BDCBD}"/>
+    <hyperlink ref="K3" r:id="rId125" xr:uid="{29450970-39DB-41B7-8010-75E800C3C8D4}"/>
+    <hyperlink ref="G3" r:id="rId126" xr:uid="{9D420FF6-4BBC-45CD-9927-70CB8B794430}"/>
+    <hyperlink ref="G22" r:id="rId127" xr:uid="{A08BBCCE-BD3A-4A78-8821-51B45070A37B}"/>
+    <hyperlink ref="G23" r:id="rId128" xr:uid="{483E5F20-7464-4538-BD04-03094D1E1AFD}"/>
+    <hyperlink ref="I23" r:id="rId129" xr:uid="{D7FF6B2D-638B-44BC-A45A-1D77702E83B0}"/>
+    <hyperlink ref="I22" r:id="rId130" xr:uid="{AB66B096-620B-4CE9-84B0-09AD5A11A798}"/>
+    <hyperlink ref="H24" r:id="rId131" xr:uid="{9ACE5488-AC37-452A-B9DB-AF9822654C3B}"/>
+    <hyperlink ref="I24" r:id="rId132" xr:uid="{42C8AF0B-279C-4881-9CF9-B8824D5BFBE8}"/>
+    <hyperlink ref="I25" r:id="rId133" xr:uid="{124B8AFE-29BB-448D-AD51-7729A6A92274}"/>
+    <hyperlink ref="G25" r:id="rId134" xr:uid="{D8D34155-7AF1-425D-94DB-9AD4A3D89FDE}"/>
+    <hyperlink ref="I26" r:id="rId135" xr:uid="{A6348DEE-52E6-439B-BF57-6AA9EB73165D}"/>
+    <hyperlink ref="G26" r:id="rId136" xr:uid="{3F56D024-33C5-407F-B594-4208C7C7CA3D}"/>
+    <hyperlink ref="G27" r:id="rId137" xr:uid="{79DD6B19-2210-4758-B339-F0F9933E7260}"/>
+    <hyperlink ref="H28" r:id="rId138" xr:uid="{9937956B-5115-49F0-B517-189F0CCEBC17}"/>
+    <hyperlink ref="H29" r:id="rId139" xr:uid="{9731DD3C-5BDB-49D1-8CE9-AB54980A8A41}"/>
+    <hyperlink ref="I29" r:id="rId140" xr:uid="{7FE2B3CA-E871-45CB-9D91-09E4E3BD2209}"/>
+    <hyperlink ref="H30" r:id="rId141" xr:uid="{B7D25D40-411E-41B4-978E-10C02CE68A0C}"/>
+    <hyperlink ref="I30" r:id="rId142" xr:uid="{0006B7F0-0FF8-48F4-87C7-B151538243AB}"/>
+    <hyperlink ref="H31" r:id="rId143" xr:uid="{A414CE39-FE1F-4289-B69F-38562E6D6904}"/>
+    <hyperlink ref="I31" r:id="rId144" xr:uid="{38ABB0A4-B872-4837-BF79-B4A63B08D9E0}"/>
+    <hyperlink ref="G32" r:id="rId145" xr:uid="{53312060-D111-4214-8544-BAE3505ADC13}"/>
+    <hyperlink ref="I32" r:id="rId146" xr:uid="{070946D8-0494-4439-925B-9965292938DB}"/>
+    <hyperlink ref="I33" r:id="rId147" xr:uid="{B7265443-833F-4E5D-8A3C-0E5640CFA14E}"/>
+    <hyperlink ref="H33" r:id="rId148" xr:uid="{3A93D353-E7D6-4B99-9F81-0B95FEBBF0CE}"/>
+    <hyperlink ref="I34" r:id="rId149" xr:uid="{562C0C97-98EA-48A6-A448-3659B7F43F6F}"/>
+    <hyperlink ref="H34" r:id="rId150" xr:uid="{7F29F009-C4B2-4160-B36E-55FE9C8DE108}"/>
+    <hyperlink ref="H35" r:id="rId151" xr:uid="{3B106540-C553-4822-BBD8-A80BBA6F8A67}"/>
+    <hyperlink ref="I36" r:id="rId152" xr:uid="{44BDAC26-3D9A-40A2-BF0B-A04D153876CF}"/>
+    <hyperlink ref="H36" r:id="rId153" xr:uid="{237F2EEA-4710-4223-82AE-70C3B6CF7AF0}"/>
+    <hyperlink ref="I37" r:id="rId154" xr:uid="{52550C92-47F1-4EF2-A1B9-E08DF54F8C75}"/>
+    <hyperlink ref="G37" r:id="rId155" xr:uid="{CFAEA637-199F-4BD8-B4DF-1D3FFEB2042A}"/>
+    <hyperlink ref="G38" r:id="rId156" xr:uid="{9A89CEC6-F4F4-49CA-943E-360F33D9C05F}"/>
+    <hyperlink ref="I38" r:id="rId157" xr:uid="{792C3B0E-A4E6-406E-96DB-F1099A72C0EF}"/>
+    <hyperlink ref="H39" r:id="rId158" xr:uid="{4920519A-420B-4C1D-9137-ABF5BF36A758}"/>
+    <hyperlink ref="I39" r:id="rId159" xr:uid="{C91CDC38-7F7C-447B-ABDA-D4EEE352EA12}"/>
+    <hyperlink ref="H40" r:id="rId160" xr:uid="{36486386-FDBB-434B-A92A-733C3891480F}"/>
+    <hyperlink ref="I40" r:id="rId161" xr:uid="{82E8640D-8F71-413D-B44B-6D328021A04A}"/>
+    <hyperlink ref="I41" r:id="rId162" xr:uid="{73080944-A3BF-4160-B555-FDB4223EBF02}"/>
+    <hyperlink ref="H42" r:id="rId163" xr:uid="{360A7008-FA04-416D-847F-77C7743D087D}"/>
+    <hyperlink ref="I42" r:id="rId164" xr:uid="{9685B4C7-737F-4376-B12F-51770912B002}"/>
+    <hyperlink ref="I43" r:id="rId165" xr:uid="{42A51A8B-430D-4882-BB92-7BB32B9EC3B4}"/>
+    <hyperlink ref="H43" r:id="rId166" xr:uid="{268827F1-F1D2-48E0-985F-98F536A13A86}"/>
+    <hyperlink ref="I44" r:id="rId167" xr:uid="{3BD89FAD-2317-4479-84E5-9D08000ABCC1}"/>
+    <hyperlink ref="H44" r:id="rId168" xr:uid="{BD54F60C-3658-466D-BFB8-F30DBE913FEB}"/>
+    <hyperlink ref="H45" r:id="rId169" xr:uid="{8EA7A96E-44D0-4F2D-89DD-4B59436BF805}"/>
+    <hyperlink ref="I45" r:id="rId170" xr:uid="{6C3DB6FA-C741-437B-ACE4-2645ECA0A0A2}"/>
+    <hyperlink ref="I46" r:id="rId171" xr:uid="{8A73320E-C545-4454-A0A7-FE6849DF947F}"/>
+    <hyperlink ref="H46" r:id="rId172" xr:uid="{FF792A0E-A603-41EE-9B12-D0F26E0AE950}"/>
+    <hyperlink ref="G47" r:id="rId173" xr:uid="{F69D80EA-3D6C-43B2-A639-A1B07EEFAD1E}"/>
+    <hyperlink ref="I47" r:id="rId174" xr:uid="{2FBF0E0E-082E-4392-8703-D9FFE03F48DB}"/>
+    <hyperlink ref="I48" r:id="rId175" xr:uid="{BE3C0C6B-3F9B-4C3B-B761-DEB35643F7C7}"/>
+    <hyperlink ref="G48" r:id="rId176" xr:uid="{75E10BFD-2507-4A0A-9BD0-C1A3CBF7EE57}"/>
+    <hyperlink ref="I49" r:id="rId177" xr:uid="{DE1FFF05-3CCB-45BE-8F2E-9209EB6C29C0}"/>
+    <hyperlink ref="H49" r:id="rId178" xr:uid="{9A4D3D1B-01AB-450A-A4C9-5D8AD5D13473}"/>
+    <hyperlink ref="I50" r:id="rId179" xr:uid="{1D67BFC3-184F-4FE9-926F-394FC48E85BF}"/>
+    <hyperlink ref="G50" r:id="rId180" xr:uid="{BB0F5B9F-8548-4CA1-BB41-95BA0E09C752}"/>
+    <hyperlink ref="G51" r:id="rId181" xr:uid="{7C329507-3CD8-47DC-9D6C-02ED91780B57}"/>
+    <hyperlink ref="I51" r:id="rId182" xr:uid="{DE8D4BEA-0C5E-494F-9CDF-35E89386A6F6}"/>
+    <hyperlink ref="G52" r:id="rId183" xr:uid="{0CC903E1-5E41-4111-9DAD-B1490CA2F312}"/>
+    <hyperlink ref="G53" r:id="rId184" xr:uid="{284ACA6D-6A22-492C-B7A3-3ADC419EFA1C}"/>
+    <hyperlink ref="H54" r:id="rId185" xr:uid="{5255DADE-DE2B-4D49-9E7B-474AF74AAC3F}"/>
+    <hyperlink ref="I55" r:id="rId186" xr:uid="{C785577A-2620-4B77-9326-1935205B6C6B}"/>
+    <hyperlink ref="H55" r:id="rId187" xr:uid="{9433CCDD-A447-49C8-A52D-9DF561FB5B79}"/>
+    <hyperlink ref="G56" r:id="rId188" xr:uid="{8B887C99-ED41-49FF-ADDF-108A37698023}"/>
+    <hyperlink ref="I56" r:id="rId189" xr:uid="{27C0E075-5E01-41D3-9831-7C026E208139}"/>
+    <hyperlink ref="I57" r:id="rId190" xr:uid="{A473A945-4AEA-4961-934E-F8FDF96A5CF0}"/>
+    <hyperlink ref="H57" r:id="rId191" xr:uid="{8F6CCB07-D35D-4931-8CA6-D1C6D9221B09}"/>
+    <hyperlink ref="H58" r:id="rId192" xr:uid="{6D9D43A8-F3E8-4FCA-AE98-CA178F5EF340}"/>
+    <hyperlink ref="I58" r:id="rId193" xr:uid="{0318FE14-789B-4A30-B628-488D0EF62717}"/>
+    <hyperlink ref="I59" r:id="rId194" xr:uid="{12ACD367-7913-4B5A-B979-6B2C13045C32}"/>
+    <hyperlink ref="H59" r:id="rId195" xr:uid="{89363B48-32EB-4FD9-AD42-3B008DC16ECC}"/>
+    <hyperlink ref="H60" r:id="rId196" xr:uid="{44BA83E7-6B2D-45FB-9E1B-ABA9462CE72A}"/>
+    <hyperlink ref="I60" r:id="rId197" xr:uid="{52A628CA-BEE8-4884-8DFA-72FFAB628F1D}"/>
+    <hyperlink ref="I61" r:id="rId198" xr:uid="{3CA6545D-67F7-4752-A37D-C8649EB1519B}"/>
+    <hyperlink ref="H61" r:id="rId199" xr:uid="{C5CAC2EE-FF96-4DB6-A0FD-603330DD048F}"/>
+    <hyperlink ref="I62" r:id="rId200" xr:uid="{EB7A3412-8E2E-45EE-B264-1BDA24FA00DC}"/>
+    <hyperlink ref="H62" r:id="rId201" xr:uid="{102CCCCE-E36B-4608-A2ED-6A88461EAD32}"/>
+    <hyperlink ref="H63" r:id="rId202" xr:uid="{DEB0983B-C46B-40D7-98A5-A601516F030C}"/>
+    <hyperlink ref="I63" r:id="rId203" xr:uid="{A7018CFA-A172-4A58-B62F-D2667DB0FAAA}"/>
+    <hyperlink ref="I64" r:id="rId204" xr:uid="{FF37EB8E-9B82-4E91-A623-B19DFADE9691}"/>
+    <hyperlink ref="H65" r:id="rId205" xr:uid="{43F705D0-9A65-4F78-ADD5-EF43D2B115ED}"/>
+    <hyperlink ref="I65" r:id="rId206" xr:uid="{67DDF291-6115-411E-90F3-5FCA82C46D07}"/>
+    <hyperlink ref="I66" r:id="rId207" xr:uid="{AFAFFE97-C4A0-4A53-96BC-221B0E0EB495}"/>
+    <hyperlink ref="H66" r:id="rId208" xr:uid="{71A36470-339C-45F0-97C4-59870BAB1800}"/>
+    <hyperlink ref="H67" r:id="rId209" xr:uid="{B542E46F-74CA-486D-AB6B-49E22E7E33AD}"/>
+    <hyperlink ref="I67" r:id="rId210" xr:uid="{5F70A2B5-417A-49FF-88A4-45F73948DC0E}"/>
+    <hyperlink ref="H68" r:id="rId211" xr:uid="{B6477C3E-0C0B-4EE4-A3FF-0F779251F9D6}"/>
+    <hyperlink ref="I68" r:id="rId212" xr:uid="{969AEE4F-87B0-407E-B833-BABBA3FE527C}"/>
+    <hyperlink ref="H69" r:id="rId213" xr:uid="{0EC72919-0858-4041-BD31-274AB257F00D}"/>
+    <hyperlink ref="I69" r:id="rId214" xr:uid="{AF42E53D-0F60-4143-B6F1-735309478748}"/>
+    <hyperlink ref="H70" r:id="rId215" xr:uid="{D994144C-7AA8-4F87-BCE3-703642981B3D}"/>
+    <hyperlink ref="I70" r:id="rId216" xr:uid="{012A9EFE-C117-45AA-BB30-685F1A261071}"/>
+    <hyperlink ref="N70" r:id="rId217" xr:uid="{774D77B5-0430-4076-9713-0BB7CB346BE7}"/>
+    <hyperlink ref="N69" r:id="rId218" xr:uid="{E09D5140-A745-45CE-B33A-B371B8C64607}"/>
+    <hyperlink ref="K22" r:id="rId219" xr:uid="{92D679AA-AC98-44ED-A5F0-F224927E9356}"/>
+    <hyperlink ref="K23" r:id="rId220" xr:uid="{E9F62591-8EE9-4998-92DA-31EBDBC44853}"/>
+    <hyperlink ref="K24" r:id="rId221" xr:uid="{C1A074D4-2F5F-4801-84C7-DB2B113C54DE}"/>
+    <hyperlink ref="K25" r:id="rId222" xr:uid="{24CBF6B9-E57E-4219-A1AF-B551EB068C3B}"/>
+    <hyperlink ref="K26" r:id="rId223" xr:uid="{4E0A9F61-9239-4156-9D6E-9A6C2BCF6362}"/>
+    <hyperlink ref="K27" r:id="rId224" xr:uid="{7DDD7074-25B0-48F5-B03C-B2DD143C9A14}"/>
+    <hyperlink ref="K28" r:id="rId225" xr:uid="{CBAD55B0-AF3E-4EC3-A376-ABD55BD9A744}"/>
+    <hyperlink ref="K29" r:id="rId226" xr:uid="{06147B81-0B2B-41B6-955F-223540232648}"/>
+    <hyperlink ref="K30" r:id="rId227" xr:uid="{A7DBE007-A1B3-4A11-8208-34F3956B6684}"/>
+    <hyperlink ref="K31" r:id="rId228" xr:uid="{DB16E36B-384A-45A4-8108-6167DF4D58D2}"/>
+    <hyperlink ref="K32" r:id="rId229" xr:uid="{7773509F-194D-434E-9815-9B9CD96F1B4A}"/>
+    <hyperlink ref="K33" r:id="rId230" xr:uid="{C4C82EE3-575F-4D87-AABE-D2B09FB81FA6}"/>
+    <hyperlink ref="K34" r:id="rId231" xr:uid="{B7BA3F8A-06F4-46E3-A6C5-DF7482F62FB2}"/>
+    <hyperlink ref="K35" r:id="rId232" xr:uid="{4268C150-1693-4BE8-8613-BA55D16ED91B}"/>
+    <hyperlink ref="K36" r:id="rId233" xr:uid="{640326C2-C7BE-4D0F-BAC5-B92897FD31ED}"/>
+    <hyperlink ref="K37" r:id="rId234" xr:uid="{AF354A09-E5E7-4880-B34F-053B60677E71}"/>
+    <hyperlink ref="K38" r:id="rId235" xr:uid="{D0A42DA3-B6C4-47C5-9AF3-07D7D84ED81C}"/>
+    <hyperlink ref="K39" r:id="rId236" xr:uid="{7B943E8D-D35C-4AEE-8D30-A284C8F20C01}"/>
+    <hyperlink ref="K40" r:id="rId237" xr:uid="{EBE20291-EE62-49AC-9129-C6F2934B943F}"/>
+    <hyperlink ref="K41" r:id="rId238" xr:uid="{C1FF2774-9DFA-4244-B748-AF9AE16F3F84}"/>
+    <hyperlink ref="K42" r:id="rId239" xr:uid="{832ACE54-5C2A-418D-8885-DDF7FE0F253A}"/>
+    <hyperlink ref="K43" r:id="rId240" xr:uid="{57E3972A-68F8-4B3B-B114-BD972770F69C}"/>
+    <hyperlink ref="K44" r:id="rId241" xr:uid="{3955EBC1-FEF0-4AF3-964F-108D07765E6C}"/>
+    <hyperlink ref="K45" r:id="rId242" xr:uid="{B6539D79-ABA4-46BA-91D8-9EF6A2CDD129}"/>
+    <hyperlink ref="K46" r:id="rId243" xr:uid="{A2053E3D-6A9A-469F-903D-32D383D0FFAF}"/>
+    <hyperlink ref="K47" r:id="rId244" xr:uid="{56F5CF9C-F452-400A-BD14-B91D4D039032}"/>
+    <hyperlink ref="K48" r:id="rId245" xr:uid="{A9B36DFF-C234-48BF-B5E5-40E91EE84062}"/>
+    <hyperlink ref="K49" r:id="rId246" xr:uid="{94744859-1786-4833-9501-7D8C92D7AACC}"/>
+    <hyperlink ref="K50" r:id="rId247" xr:uid="{721A79C2-6C7E-4C1C-A283-E2C6523CF464}"/>
+    <hyperlink ref="K51" r:id="rId248" xr:uid="{3155EFF4-85FB-4171-82F3-F4FEF14E8F3C}"/>
+    <hyperlink ref="K52" r:id="rId249" xr:uid="{88739B09-EFBF-4415-AEF0-0A2F4EC05E66}"/>
+    <hyperlink ref="K53" r:id="rId250" xr:uid="{67D52B33-95C2-4585-A046-0C6F9B0B8D5B}"/>
+    <hyperlink ref="K54" r:id="rId251" xr:uid="{6AC0C8D4-4727-4BC9-9ED9-DCC8F548F82B}"/>
+    <hyperlink ref="K55" r:id="rId252" xr:uid="{C1D85E40-83E2-48BD-ABD3-E19251AFA2E2}"/>
+    <hyperlink ref="K56" r:id="rId253" xr:uid="{4FE3D899-817D-42D5-84EC-7FA4B94D10FF}"/>
+    <hyperlink ref="K57" r:id="rId254" xr:uid="{6A81878E-6BED-4415-8B2E-311785BBBA3C}"/>
+    <hyperlink ref="K58" r:id="rId255" xr:uid="{F6CE14BA-880C-455B-B447-BCBCF0220BCF}"/>
+    <hyperlink ref="K59" r:id="rId256" xr:uid="{A2A5637F-D312-49D2-8258-5795462AE4DE}"/>
+    <hyperlink ref="K60" r:id="rId257" xr:uid="{F4DA95F7-4F6D-4398-841E-C515F8EEB1E4}"/>
+    <hyperlink ref="K61" r:id="rId258" xr:uid="{ACAA867E-D445-4528-B5D2-02BA6A6F1779}"/>
+    <hyperlink ref="K62" r:id="rId259" xr:uid="{94631832-2396-4F59-A9C8-3AC80F5A167B}"/>
+    <hyperlink ref="K63" r:id="rId260" xr:uid="{00FE511F-767B-4392-B69D-D8413969EE3C}"/>
+    <hyperlink ref="K64" r:id="rId261" xr:uid="{0B4C561E-33C5-4A52-871E-F4F4DEDF73AC}"/>
+    <hyperlink ref="K65" r:id="rId262" xr:uid="{5AAF75E4-3DA5-4D86-8DAE-C6ECD44F2390}"/>
+    <hyperlink ref="K66" r:id="rId263" xr:uid="{F0BBE0AD-88AA-4284-85B5-B8668C71F53C}"/>
+    <hyperlink ref="K67" r:id="rId264" xr:uid="{EDF52BEC-A677-4BDA-BE78-EF693942CE38}"/>
+    <hyperlink ref="K68" r:id="rId265" xr:uid="{F71807C8-D7EC-4830-B41C-F58DFE8ADFE3}"/>
+    <hyperlink ref="K69" r:id="rId266" xr:uid="{D9481A01-E888-44B9-A550-B25FD0C40144}"/>
+    <hyperlink ref="K70" r:id="rId267" xr:uid="{48501ED3-8A1F-46A6-AF34-EA1086A21E9E}"/>
+    <hyperlink ref="K75" r:id="rId268" xr:uid="{A616A30C-336A-441E-AEA8-AA6A45A372CC}"/>
+    <hyperlink ref="K71" r:id="rId269" xr:uid="{F392E331-605B-4657-BD9F-B92B4FC52DF2}"/>
+    <hyperlink ref="K72" r:id="rId270" xr:uid="{E87EAE23-E8B5-46EE-8506-078EDC4ECE18}"/>
+    <hyperlink ref="K73" r:id="rId271" xr:uid="{EC336D72-89F6-41E5-8D45-559B001CD3C5}"/>
+    <hyperlink ref="K74" r:id="rId272" xr:uid="{3EBC7866-56B5-45E7-AB20-C579CADD97B9}"/>
+    <hyperlink ref="N71" r:id="rId273" xr:uid="{C287E580-B43F-4161-AEEE-04FD434E8001}"/>
+    <hyperlink ref="N72" r:id="rId274" xr:uid="{8AC448D2-E0F2-48CE-A37E-3DCFE279C06B}"/>
+    <hyperlink ref="N73" r:id="rId275" xr:uid="{AD2FD7FC-9B1B-4C96-8E6A-031D76E5CC9B}"/>
+    <hyperlink ref="N74" r:id="rId276" xr:uid="{0CC50197-D061-4F15-BCEE-7D6B573344AD}"/>
+    <hyperlink ref="H71" r:id="rId277" xr:uid="{1FB76FBF-2338-4060-8E55-16BB79A419A2}"/>
+    <hyperlink ref="H72" r:id="rId278" xr:uid="{CD9A450D-0019-4A6D-95A9-F720BCFF88C5}"/>
+    <hyperlink ref="I72" r:id="rId279" xr:uid="{3FFA0B44-F641-47D6-B287-5BE3CA6C5AB5}"/>
+    <hyperlink ref="I73" r:id="rId280" xr:uid="{F093AA87-D916-4BB2-A320-8EFA680376A4}"/>
+    <hyperlink ref="H73" r:id="rId281" xr:uid="{5F6284C0-96CC-4477-9087-191AA35E2902}"/>
+    <hyperlink ref="I74" r:id="rId282" xr:uid="{9D47BD05-3F5C-4E13-8A2F-A665282E584B}"/>
+    <hyperlink ref="N75" r:id="rId283" xr:uid="{EBD5380E-DB80-4BF6-A61E-A6309E93235F}"/>
+    <hyperlink ref="H75" r:id="rId284" xr:uid="{E433EC64-4484-4CBF-8E20-D04AC76381E6}"/>
+    <hyperlink ref="N76" r:id="rId285" xr:uid="{9BB80CDF-1F45-4D34-B964-732422A85FA1}"/>
+    <hyperlink ref="H76" r:id="rId286" xr:uid="{8AE9BF4A-ADDA-4003-A9EC-FF03F3FD45A6}"/>
+    <hyperlink ref="K76" r:id="rId287" xr:uid="{38147578-3C56-41DE-A433-6C76966FDFB5}"/>
+    <hyperlink ref="N77" r:id="rId288" xr:uid="{CB63072D-008E-41FC-B36A-9E78F25CD01B}"/>
+    <hyperlink ref="K77" r:id="rId289" xr:uid="{B800310B-1B67-4F88-97E8-A365C5550B80}"/>
+    <hyperlink ref="G77" r:id="rId290" xr:uid="{849C2ED3-ABCA-4199-BD76-F2AA46588337}"/>
+    <hyperlink ref="N78" r:id="rId291" xr:uid="{BF91105E-213D-493B-8DC6-5D25FC41317E}"/>
+    <hyperlink ref="G79" r:id="rId292" xr:uid="{5641DEA3-15F1-4209-8713-65610EDDB9DC}"/>
+    <hyperlink ref="N79" r:id="rId293" xr:uid="{52D13C80-AB6F-4E9D-AFE3-9898D895534A}"/>
+    <hyperlink ref="K79" r:id="rId294" xr:uid="{00DFBABA-EB23-4041-907B-3FC94D925FB5}"/>
+    <hyperlink ref="I79" r:id="rId295" xr:uid="{0779BC2F-DA16-4077-BF98-E185BA09732E}"/>
+    <hyperlink ref="G78" r:id="rId296" xr:uid="{032C2BC7-0200-485A-9D2D-FD7AF2EA2CAE}"/>
+    <hyperlink ref="K80" r:id="rId297" xr:uid="{00A3006D-6ACD-4C6B-A933-44D9086C0EDC}"/>
+    <hyperlink ref="G80" r:id="rId298" xr:uid="{0E83526C-5F05-4E74-A7C4-93345DE5F738}"/>
+    <hyperlink ref="N80" r:id="rId299" xr:uid="{25F31BFD-BF9A-487F-BDDC-2B60C7AC82CB}"/>
+    <hyperlink ref="K78" r:id="rId300" xr:uid="{A9AF548A-4521-4D15-A568-5A93F4674F41}"/>
+    <hyperlink ref="K81" r:id="rId301" xr:uid="{620438B4-4399-41D0-9E7A-A8F5C8F98873}"/>
+    <hyperlink ref="N81" r:id="rId302" xr:uid="{A3FE875F-164C-4AB7-9364-BCBAE50C4C80}"/>
+    <hyperlink ref="H81" r:id="rId303" xr:uid="{E1504402-A324-4050-92C0-8B9DB6592AE1}"/>
+    <hyperlink ref="H20" r:id="rId304" xr:uid="{8AFB364F-9BB5-4C05-B152-6C2BC97CB545}"/>
+    <hyperlink ref="H74" r:id="rId305" xr:uid="{9408BB90-4BA1-4555-BE41-D136FD900104}"/>
+    <hyperlink ref="I81" r:id="rId306" xr:uid="{5D38C687-BAC7-4B47-84E3-6B00E74770B3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId308"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId307"/>
   <ignoredErrors>
-    <ignoredError sqref="E3:E54 F3:F54 E2:F2 E55:E70 F55:F70 E71:F71 E72:F74 E75:F77 E78:F80" numberStoredAsText="1"/>
+    <ignoredError sqref="E3:E54 F3:F54 E2:F2 E55:E70 F55:F70 E71:F71 E72:F74 E75:F77 E78:F81" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8621,7 +8727,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -8636,632 +8742,632 @@
       <c r="L1" s="30"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>914</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
+      <c r="A2" s="32" t="s">
+        <v>900</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
     </row>
     <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>880</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="29" t="s">
+        <v>868</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>859</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+    </row>
+    <row r="4" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>869</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>889</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+    </row>
+    <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>870</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>860</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+    </row>
+    <row r="6" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>871</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-    </row>
-    <row r="4" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
-        <v>881</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>901</v>
-      </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-    </row>
-    <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
-        <v>882</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="B6" s="31" t="s">
+        <v>861</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+    </row>
+    <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>908</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>890</v>
+      </c>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+    </row>
+    <row r="8" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
         <v>872</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-    </row>
-    <row r="6" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
-        <v>883</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>873</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-    </row>
-    <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
-        <v>922</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>902</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-    </row>
-    <row r="8" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
-        <v>884</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>874</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
+      <c r="B8" s="31" t="s">
+        <v>862</v>
+      </c>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>885</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>903</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
+        <v>873</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>891</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>886</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>904</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
+        <v>874</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>892</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>887</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>905</v>
-      </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
+        <v>875</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>893</v>
+      </c>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>888</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>906</v>
-      </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
+        <v>876</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>894</v>
+      </c>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>890</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>875</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
+        <v>878</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>863</v>
+      </c>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
-        <v>889</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>907</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
+      <c r="A14" s="29" t="s">
+        <v>877</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>927</v>
+      </c>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
     </row>
     <row r="15" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>891</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>876</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
+        <v>879</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>864</v>
+      </c>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>892</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>908</v>
-      </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
+        <v>880</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>895</v>
+      </c>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>893</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>909</v>
-      </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
+        <v>881</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>896</v>
+      </c>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>894</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>877</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
+        <v>882</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>865</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>895</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>910</v>
-      </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-    </row>
-    <row r="20" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>883</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>897</v>
+      </c>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+    </row>
+    <row r="20" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>896</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>911</v>
-      </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
+        <v>884</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>928</v>
+      </c>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>897</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>878</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
+        <v>885</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>866</v>
+      </c>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
     </row>
     <row r="22" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
+        <v>886</v>
+      </c>
+      <c r="B22" s="33" t="s">
         <v>898</v>
       </c>
-      <c r="B22" s="29" t="s">
-        <v>912</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
     </row>
     <row r="23" spans="1:12" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
+        <v>887</v>
+      </c>
+      <c r="B23" s="33" t="s">
         <v>899</v>
       </c>
-      <c r="B23" s="29" t="s">
-        <v>913</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
     </row>
     <row r="24" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>900</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>879</v>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
+        <v>888</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>867</v>
+      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
     </row>
     <row r="25" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>916</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>929</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
+        <v>902</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>915</v>
+      </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
     </row>
     <row r="26" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>917</v>
-      </c>
-      <c r="B26" s="29" t="s">
-        <v>930</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
+        <v>903</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>916</v>
+      </c>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
     </row>
     <row r="27" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>918</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>931</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
+        <v>904</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>917</v>
+      </c>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
     </row>
     <row r="28" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>919</v>
-      </c>
-      <c r="B28" s="29" t="s">
-        <v>932</v>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
+        <v>905</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>918</v>
+      </c>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
     </row>
     <row r="29" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>920</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>933</v>
-      </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
+        <v>906</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>919</v>
+      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
     </row>
     <row r="30" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>921</v>
-      </c>
-      <c r="B30" s="29" t="s">
-        <v>934</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
+        <v>907</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>920</v>
+      </c>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
     </row>
     <row r="31" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>923</v>
-      </c>
-      <c r="B31" s="29" t="s">
-        <v>935</v>
-      </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
+        <v>909</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>921</v>
+      </c>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
     </row>
     <row r="32" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>927</v>
-      </c>
-      <c r="B32" s="29" t="s">
-        <v>940</v>
-      </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
+        <v>913</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>926</v>
+      </c>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
     </row>
     <row r="33" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
-        <v>924</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>936</v>
-      </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
+        <v>910</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>922</v>
+      </c>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>925</v>
-      </c>
-      <c r="B34" s="29" t="s">
-        <v>937</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="29"/>
+        <v>911</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>923</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
     </row>
     <row r="35" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
-        <v>926</v>
-      </c>
-      <c r="B35" s="29" t="s">
-        <v>938</v>
-      </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
+        <v>912</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>924</v>
+      </c>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
     </row>
     <row r="36" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>928</v>
-      </c>
-      <c r="B36" s="29" t="s">
-        <v>939</v>
-      </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
+        <v>914</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>925</v>
+      </c>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -9284,6 +9390,7 @@
     <mergeCell ref="B14:L14"/>
     <mergeCell ref="B15:L15"/>
     <mergeCell ref="B16:L16"/>
+    <mergeCell ref="B11:L11"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B18:L18"/>
     <mergeCell ref="B19:L19"/>
@@ -9295,7 +9402,6 @@
     <mergeCell ref="B25:L25"/>
     <mergeCell ref="B26:L26"/>
     <mergeCell ref="B27:L27"/>
-    <mergeCell ref="B11:L11"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B4:L4"/>

--- a/hiedra-filosofas-mapa-listo.xlsx
+++ b/hiedra-filosofas-mapa-listo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nati\OneDrive\Escritorio\La_hiedra_en_la_grieta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40C5C96-0F24-4C85-8BA0-83EC6C8BB673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2457E5BC-A64F-4C4C-8B30-A3B6D22E1956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="255" windowWidth="19080" windowHeight="10545" xr2:uid="{710D68A0-BE3B-4DEE-ABF3-33E9BEF5963F}"/>
+    <workbookView xWindow="780" yWindow="255" windowWidth="19080" windowHeight="10545" activeTab="1" xr2:uid="{710D68A0-BE3B-4DEE-ABF3-33E9BEF5963F}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapa" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="943">
   <si>
     <t>Fecha de nacimiento</t>
   </si>
@@ -4254,12 +4254,6 @@
     <t>Término acuñado por Carole Pateman para denunciar que el contrato social liberal esconde un pacto patriarcal implícito que subyugó a las mujeres desde el principio. Según esta teoría, los contratos civiles (como el matrimonio) están diseñados para asegurar el derecho sexual y reproductivo de los hombres, manteniendo a las mujeres subordinadas e inhibiendo su autonomía.</t>
   </si>
   <si>
-    <t>Conjunto de normas y prácticas sociales que asumen la heterosexualidad y la familia nuclear heterosexual como modelo "natural" o normal. En una matriz heteronormativa se presupone que la orientación sexual y la identidad de género deben alinearse (sexo-biológico masculino = identidad masculina, relaciones heterosexuales, roles tradicionales, etc.). Esto invisibiliza y margina otras identidades sexuales y de género, relegándolas como "anormales" en la cultura dominante.</t>
-  </si>
-  <si>
-    <t>Idea (acepción crítica) de que a las mujeres les corresponde por naturaleza una tarea reproductiva obligatoria, como la maternidad y el cuidado. En el feminismo se rechaza esta "obligación biológica": se argumenta que los roles reproductivos no son meramente inescapables por biología, sino que están influidos por factores sociales y deben ser una elección.</t>
-  </si>
-  <si>
     <t>Doctrina según la cual el comportamiento humano y las diferencias sociales (incluyendo la desigualdad de género) están fijados por la biología heredada; es decir, las normas y jerarquías sociales reflejan diferencias innatas entre individuos. El determinismo biológico afirma que rasgos y roles sociales dependen de los genes, idea que las ciencias contemporáneas rechazan, pues reconocen la compleja interacción entre biología y ambiente.</t>
   </si>
   <si>
@@ -4278,9 +4272,6 @@
     <t>Constructo social</t>
   </si>
   <si>
-    <t>Innatas</t>
-  </si>
-  <si>
     <t>Relaciones de poder</t>
   </si>
   <si>
@@ -4317,13 +4308,7 @@
     <t>Entidad o idea creada culturalmente que no existe por sí sola en la naturaleza, sino por acuerdo convencional. Se sostiene porque la sociedad acepta reglas o normas que le dan existencia.</t>
   </si>
   <si>
-    <t>Cualidades o comportamientos presentes desde el nacimiento, sin necesidad de aprendizaje, ligados a la dotación biológica heredada.</t>
-  </si>
-  <si>
     <t>Dinámicas sociales en las que individuos o grupos ejercen control, autoridad o influencia sobre otros, determinando desigualdades y jerarquías en la sociedad.</t>
-  </si>
-  <si>
-    <t>Término del derecho romano que designa al "jefe o cabeza de familia" (siempre varón). En contextos patriarcales, simboliza la autoridad paterna tradicional.</t>
   </si>
   <si>
     <t>Forma de masculinidad dominante que legitima el patriarcado. Según Connell, es la configuración culturalmente idealizada de la masculinidad que sostiene la posición social superior de los hombres y la subordinación de las mujeres.</t>
@@ -4417,6 +4402,15 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=ZqwlLHju9vo</t>
+  </si>
+  <si>
+    <t>Término del derecho romano que designa al jefe o cabeza de familia (siempre varón). En contextos patriarcales, simboliza la autoridad paterna tradicional.</t>
+  </si>
+  <si>
+    <t>Idea (acepción crítica) de que a las mujeres les corresponde por naturaleza una tarea reproductiva obligatoria, como la maternidad y el cuidado. En el feminismo se rechaza esta obligación biológica: se argumenta que los roles reproductivos no son meramente inescapables por biología, sino que están influidos por factores sociales y deben ser una elección.</t>
+  </si>
+  <si>
+    <t>Conjunto de normas y prácticas sociales que asumen la heterosexualidad y la familia nuclear heterosexual como modelo natural o normal. En una matriz heteronormativa se presupone que la orientación sexual y la identidad de género deben alinearse (sexo-biológico masculino = identidad masculina, relaciones heterosexuales, roles tradicionales, etc.). Esto invisibiliza y margina otras identidades sexuales y de género, relegándolas como anormales en la cultura dominante.</t>
   </si>
 </sst>
 </file>
@@ -4493,7 +4487,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4650,19 +4644,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4698,6 +4679,19 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5257,14 +5251,14 @@
       <c r="E6" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="30" t="s">
         <v>223</v>
       </c>
       <c r="G6" s="14"/>
       <c r="H6" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I6" s="34"/>
+      <c r="I6" s="29"/>
       <c r="J6" s="6" t="s">
         <v>127</v>
       </c>
@@ -5701,7 +5695,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" s="33" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>20</v>
       </c>
@@ -5714,15 +5708,15 @@
       <c r="D17" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="36" t="s">
-        <v>938</v>
+      <c r="G17" s="29"/>
+      <c r="H17" s="31" t="s">
+        <v>933</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>169</v>
@@ -5739,7 +5733,7 @@
       <c r="M17" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="N17" s="37" t="s">
+      <c r="N17" s="32" t="s">
         <v>170</v>
       </c>
     </row>
@@ -5827,7 +5821,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="38" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" s="33" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>26</v>
       </c>
@@ -5840,23 +5834,23 @@
       <c r="D20" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F20" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="36" t="s">
-        <v>940</v>
+      <c r="G20" s="29"/>
+      <c r="H20" s="31" t="s">
+        <v>935</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="J20" s="40" t="s">
+      <c r="J20" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="K20" s="37" t="s">
+      <c r="K20" s="32" t="s">
         <v>251</v>
       </c>
       <c r="L20" s="13" t="s">
@@ -5865,8 +5859,8 @@
       <c r="M20" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="N20" s="41" t="s">
-        <v>937</v>
+      <c r="N20" s="36" t="s">
+        <v>932</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5953,36 +5947,36 @@
         <v>272</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="38" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" s="33" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="34" t="s">
+      <c r="D23" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="30" t="s">
         <v>414</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="30" t="s">
         <v>415</v>
       </c>
-      <c r="G23" s="36" t="s">
-        <v>939</v>
-      </c>
-      <c r="H23" s="34"/>
-      <c r="I23" s="36" t="s">
+      <c r="G23" s="31" t="s">
+        <v>934</v>
+      </c>
+      <c r="H23" s="29"/>
+      <c r="I23" s="31" t="s">
         <v>522</v>
       </c>
       <c r="J23" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="K23" s="36" t="s">
+      <c r="K23" s="31" t="s">
         <v>625</v>
       </c>
       <c r="L23" s="13" t="s">
@@ -5991,7 +5985,7 @@
       <c r="M23" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="N23" s="37" t="s">
+      <c r="N23" s="32" t="s">
         <v>273</v>
       </c>
     </row>
@@ -6919,7 +6913,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="46" spans="1:14" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" s="33" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>438</v>
       </c>
@@ -6932,23 +6926,23 @@
       <c r="D46" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="E46" s="35" t="s">
+      <c r="E46" s="30" t="s">
         <v>474</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F46" s="30" t="s">
         <v>475</v>
       </c>
-      <c r="G46" s="34"/>
-      <c r="H46" s="36" t="s">
-        <v>944</v>
-      </c>
-      <c r="I46" s="36" t="s">
+      <c r="G46" s="29"/>
+      <c r="H46" s="31" t="s">
+        <v>939</v>
+      </c>
+      <c r="I46" s="31" t="s">
         <v>572</v>
       </c>
       <c r="J46" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="K46" s="36" t="s">
+      <c r="K46" s="31" t="s">
         <v>728</v>
       </c>
       <c r="L46" s="13" t="s">
@@ -6957,7 +6951,7 @@
       <c r="M46" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="N46" s="37" t="s">
+      <c r="N46" s="32" t="s">
         <v>298</v>
       </c>
     </row>
@@ -7187,14 +7181,14 @@
       <c r="E52" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="F52" s="35" t="s">
+      <c r="F52" s="30" t="s">
         <v>488</v>
       </c>
-      <c r="G52" s="36" t="s">
+      <c r="G52" s="31" t="s">
         <v>583</v>
       </c>
-      <c r="H52" s="36"/>
-      <c r="I52" s="34"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="29"/>
       <c r="J52" s="6" t="s">
         <v>739</v>
       </c>
@@ -7211,7 +7205,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="53" spans="1:14" s="38" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" s="33" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>44</v>
       </c>
@@ -7221,24 +7215,24 @@
       <c r="C53" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="29" t="s">
         <v>432</v>
       </c>
-      <c r="E53" s="35" t="s">
+      <c r="E53" s="30" t="s">
         <v>489</v>
       </c>
-      <c r="F53" s="35" t="s">
+      <c r="F53" s="30" t="s">
         <v>490</v>
       </c>
-      <c r="G53" s="36" t="s">
+      <c r="G53" s="31" t="s">
         <v>584</v>
       </c>
-      <c r="H53" s="36"/>
-      <c r="I53" s="34"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="29"/>
       <c r="J53" s="13" t="s">
         <v>741</v>
       </c>
-      <c r="K53" s="36" t="s">
+      <c r="K53" s="31" t="s">
         <v>742</v>
       </c>
       <c r="L53" s="13" t="s">
@@ -7247,7 +7241,7 @@
       <c r="M53" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="N53" s="37" t="s">
+      <c r="N53" s="32" t="s">
         <v>305</v>
       </c>
     </row>
@@ -7267,14 +7261,14 @@
       <c r="E54" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="F54" s="35" t="s">
+      <c r="F54" s="30" t="s">
         <v>492</v>
       </c>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36" t="s">
+      <c r="G54" s="31"/>
+      <c r="H54" s="31" t="s">
         <v>585</v>
       </c>
-      <c r="I54" s="34"/>
+      <c r="I54" s="29"/>
       <c r="J54" s="6" t="s">
         <v>743</v>
       </c>
@@ -7375,36 +7369,36 @@
         <v>308</v>
       </c>
     </row>
-    <row r="57" spans="1:14" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" s="33" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B57" s="13">
         <v>1953</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D57" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E57" s="35" t="s">
+      <c r="E57" s="30" t="s">
         <v>497</v>
       </c>
-      <c r="F57" s="35" t="s">
+      <c r="F57" s="30" t="s">
         <v>498</v>
       </c>
       <c r="G57" s="13"/>
-      <c r="H57" s="36" t="s">
+      <c r="H57" s="31" t="s">
         <v>591</v>
       </c>
-      <c r="I57" s="36" t="s">
+      <c r="I57" s="31" t="s">
         <v>590</v>
       </c>
       <c r="J57" s="13" t="s">
         <v>749</v>
       </c>
-      <c r="K57" s="36" t="s">
+      <c r="K57" s="31" t="s">
         <v>750</v>
       </c>
       <c r="L57" s="13" t="s">
@@ -7413,7 +7407,7 @@
       <c r="M57" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="N57" s="37" t="s">
+      <c r="N57" s="32" t="s">
         <v>309</v>
       </c>
     </row>
@@ -7753,7 +7747,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="66" spans="1:14" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" s="33" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
         <v>192</v>
       </c>
@@ -7766,23 +7760,23 @@
       <c r="D66" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="E66" s="35" t="s">
+      <c r="E66" s="30" t="s">
         <v>515</v>
       </c>
-      <c r="F66" s="35" t="s">
+      <c r="F66" s="30" t="s">
         <v>516</v>
       </c>
-      <c r="G66" s="34"/>
-      <c r="H66" s="36" t="s">
-        <v>941</v>
-      </c>
-      <c r="I66" s="36" t="s">
+      <c r="G66" s="29"/>
+      <c r="H66" s="31" t="s">
+        <v>936</v>
+      </c>
+      <c r="I66" s="31" t="s">
         <v>607</v>
       </c>
       <c r="J66" s="13" t="s">
         <v>767</v>
       </c>
-      <c r="K66" s="36" t="s">
+      <c r="K66" s="31" t="s">
         <v>768</v>
       </c>
       <c r="L66" s="13" t="s">
@@ -7791,7 +7785,7 @@
       <c r="M66" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="N66" s="37" t="s">
+      <c r="N66" s="32" t="s">
         <v>319</v>
       </c>
     </row>
@@ -7960,41 +7954,41 @@
         <v>620</v>
       </c>
     </row>
-    <row r="71" spans="1:14" s="38" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="38" t="s">
+    <row r="71" spans="1:14" s="33" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="33" t="s">
         <v>671</v>
       </c>
-      <c r="B71" s="42"/>
-      <c r="C71" s="42" t="s">
+      <c r="B71" s="37"/>
+      <c r="C71" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="D71" s="42" t="s">
+      <c r="D71" s="37" t="s">
         <v>430</v>
       </c>
-      <c r="E71" s="43" t="s">
+      <c r="E71" s="38" t="s">
         <v>677</v>
       </c>
-      <c r="F71" s="43" t="s">
+      <c r="F71" s="38" t="s">
         <v>678</v>
       </c>
-      <c r="G71" s="34"/>
-      <c r="H71" s="41" t="s">
-        <v>942</v>
-      </c>
-      <c r="I71" s="34"/>
-      <c r="J71" s="44" t="s">
+      <c r="G71" s="29"/>
+      <c r="H71" s="36" t="s">
+        <v>937</v>
+      </c>
+      <c r="I71" s="29"/>
+      <c r="J71" s="39" t="s">
         <v>778</v>
       </c>
-      <c r="K71" s="41" t="s">
+      <c r="K71" s="36" t="s">
         <v>781</v>
       </c>
-      <c r="L71" s="42" t="s">
+      <c r="L71" s="37" t="s">
         <v>670</v>
       </c>
-      <c r="M71" s="42" t="s">
+      <c r="M71" s="37" t="s">
         <v>788</v>
       </c>
-      <c r="N71" s="41" t="s">
+      <c r="N71" s="36" t="s">
         <v>792</v>
       </c>
     </row>
@@ -8076,43 +8070,43 @@
         <v>794</v>
       </c>
     </row>
-    <row r="74" spans="1:14" s="38" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="38" t="s">
+    <row r="74" spans="1:14" s="33" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="33" t="s">
         <v>623</v>
       </c>
-      <c r="B74" s="42"/>
-      <c r="C74" s="42" t="s">
+      <c r="B74" s="37"/>
+      <c r="C74" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="D74" s="42" t="s">
+      <c r="D74" s="37" t="s">
         <v>430</v>
       </c>
-      <c r="E74" s="43" t="s">
+      <c r="E74" s="38" t="s">
         <v>681</v>
       </c>
-      <c r="F74" s="43" t="s">
+      <c r="F74" s="38" t="s">
         <v>682</v>
       </c>
-      <c r="G74" s="34"/>
-      <c r="H74" s="45" t="s">
+      <c r="G74" s="29"/>
+      <c r="H74" s="40" t="s">
         <v>800</v>
       </c>
-      <c r="I74" s="41" t="s">
+      <c r="I74" s="36" t="s">
         <v>800</v>
       </c>
-      <c r="J74" s="44" t="s">
+      <c r="J74" s="39" t="s">
         <v>787</v>
       </c>
-      <c r="K74" s="41" t="s">
+      <c r="K74" s="36" t="s">
         <v>786</v>
       </c>
-      <c r="L74" s="42" t="s">
+      <c r="L74" s="37" t="s">
         <v>676</v>
       </c>
-      <c r="M74" s="42" t="s">
+      <c r="M74" s="37" t="s">
         <v>791</v>
       </c>
-      <c r="N74" s="41" t="s">
+      <c r="N74" s="36" t="s">
         <v>795</v>
       </c>
     </row>
@@ -8129,18 +8123,18 @@
       <c r="D75" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="E75" s="43" t="s">
+      <c r="E75" s="38" t="s">
         <v>806</v>
       </c>
-      <c r="F75" s="43" t="s">
+      <c r="F75" s="38" t="s">
         <v>807</v>
       </c>
-      <c r="G75" s="36"/>
-      <c r="H75" s="41" t="s">
+      <c r="G75" s="31"/>
+      <c r="H75" s="36" t="s">
         <v>802</v>
       </c>
-      <c r="I75" s="34"/>
-      <c r="J75" s="44" t="s">
+      <c r="I75" s="29"/>
+      <c r="J75" s="39" t="s">
         <v>779</v>
       </c>
       <c r="K75" s="27" t="s">
@@ -8166,18 +8160,18 @@
       <c r="D76" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="E76" s="43" t="s">
+      <c r="E76" s="38" t="s">
         <v>804</v>
       </c>
-      <c r="F76" s="43" t="s">
+      <c r="F76" s="38" t="s">
         <v>805</v>
       </c>
-      <c r="G76" s="34"/>
-      <c r="H76" s="41" t="s">
+      <c r="G76" s="29"/>
+      <c r="H76" s="36" t="s">
         <v>810</v>
       </c>
-      <c r="I76" s="34"/>
-      <c r="J76" s="44" t="s">
+      <c r="I76" s="29"/>
+      <c r="J76" s="39" t="s">
         <v>809</v>
       </c>
       <c r="K76" s="27" t="s">
@@ -8206,18 +8200,18 @@
       <c r="D77" s="21" t="s">
         <v>817</v>
       </c>
-      <c r="E77" s="43" t="s">
+      <c r="E77" s="38" t="s">
         <v>830</v>
       </c>
-      <c r="F77" s="43" t="s">
+      <c r="F77" s="38" t="s">
         <v>831</v>
       </c>
-      <c r="G77" s="41" t="s">
+      <c r="G77" s="36" t="s">
         <v>829</v>
       </c>
-      <c r="H77" s="41"/>
-      <c r="I77" s="34"/>
-      <c r="J77" s="44" t="s">
+      <c r="H77" s="36"/>
+      <c r="I77" s="29"/>
+      <c r="J77" s="39" t="s">
         <v>827</v>
       </c>
       <c r="K77" s="27" t="s">
@@ -8246,18 +8240,18 @@
       <c r="D78" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="E78" s="43" t="s">
+      <c r="E78" s="38" t="s">
         <v>832</v>
       </c>
-      <c r="F78" s="43" t="s">
+      <c r="F78" s="38" t="s">
         <v>833</v>
       </c>
-      <c r="G78" s="36" t="s">
+      <c r="G78" s="31" t="s">
         <v>844</v>
       </c>
-      <c r="H78" s="34"/>
-      <c r="I78" s="34"/>
-      <c r="J78" s="44" t="s">
+      <c r="H78" s="29"/>
+      <c r="I78" s="29"/>
+      <c r="J78" s="39" t="s">
         <v>856</v>
       </c>
       <c r="K78" s="27" t="s">
@@ -8286,20 +8280,20 @@
       <c r="D79" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="E79" s="43" t="s">
+      <c r="E79" s="38" t="s">
         <v>834</v>
       </c>
-      <c r="F79" s="43" t="s">
+      <c r="F79" s="38" t="s">
         <v>835</v>
       </c>
-      <c r="G79" s="36" t="s">
+      <c r="G79" s="31" t="s">
         <v>837</v>
       </c>
-      <c r="H79" s="34"/>
-      <c r="I79" s="41" t="s">
+      <c r="H79" s="29"/>
+      <c r="I79" s="36" t="s">
         <v>841</v>
       </c>
-      <c r="J79" s="44" t="s">
+      <c r="J79" s="39" t="s">
         <v>839</v>
       </c>
       <c r="K79" s="27" t="s">
@@ -8356,8 +8350,8 @@
       </c>
     </row>
     <row r="81" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="38" t="s">
-        <v>901</v>
+      <c r="A81" s="33" t="s">
+        <v>899</v>
       </c>
       <c r="B81" s="21">
         <v>1944</v>
@@ -8369,31 +8363,31 @@
         <v>83</v>
       </c>
       <c r="E81" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="F81" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="H81" s="27" t="s">
+        <v>930</v>
+      </c>
+      <c r="I81" s="34" t="s">
+        <v>938</v>
+      </c>
+      <c r="J81" s="23" t="s">
+        <v>926</v>
+      </c>
+      <c r="K81" s="27" t="s">
+        <v>927</v>
+      </c>
+      <c r="L81" s="21" t="s">
         <v>929</v>
       </c>
-      <c r="F81" s="22" t="s">
-        <v>930</v>
-      </c>
-      <c r="H81" s="27" t="s">
-        <v>935</v>
-      </c>
-      <c r="I81" s="39" t="s">
-        <v>943</v>
-      </c>
-      <c r="J81" s="23" t="s">
+      <c r="M81" s="21" t="s">
         <v>931</v>
       </c>
-      <c r="K81" s="27" t="s">
-        <v>932</v>
-      </c>
-      <c r="L81" s="21" t="s">
-        <v>934</v>
-      </c>
-      <c r="M81" s="21" t="s">
-        <v>936</v>
-      </c>
       <c r="N81" s="27" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
@@ -8718,7 +8712,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37DB1C-6366-43BC-87B4-D48265439827}">
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
@@ -8726,659 +8720,648 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="42" t="s">
         <v>858</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>900</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
+      <c r="A2" s="43" t="s">
+        <v>898</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
     </row>
     <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="44" t="s">
         <v>868</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="45" t="s">
         <v>859</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
     </row>
     <row r="4" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="44" t="s">
         <v>869</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="45" t="s">
         <v>889</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
     </row>
     <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="44" t="s">
         <v>870</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="45" t="s">
         <v>860</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
     </row>
     <row r="6" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="44" t="s">
         <v>871</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="45" t="s">
         <v>861</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
     </row>
     <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>908</v>
-      </c>
-      <c r="B7" s="31" t="s">
+      <c r="A7" s="44" t="s">
+        <v>905</v>
+      </c>
+      <c r="B7" s="45" t="s">
         <v>890</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
     </row>
     <row r="8" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="44" t="s">
         <v>872</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="45" t="s">
         <v>862</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>873</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="41" t="s">
         <v>891</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
     </row>
     <row r="10" spans="1:12" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>874</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="41" t="s">
         <v>892</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
     </row>
     <row r="11" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>875</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="41" t="s">
         <v>893</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
     </row>
     <row r="12" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>876</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="41" t="s">
         <v>894</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>878</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="41" t="s">
         <v>863</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
     </row>
     <row r="14" spans="1:12" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="44" t="s">
         <v>877</v>
       </c>
-      <c r="B14" s="31" t="s">
-        <v>927</v>
-      </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
+      <c r="B14" s="45" t="s">
+        <v>922</v>
+      </c>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45"/>
     </row>
     <row r="15" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>879</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="41" t="s">
         <v>864</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
     </row>
     <row r="16" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
         <v>880</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="41" t="s">
         <v>895</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
     </row>
     <row r="17" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
         <v>881</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="41" t="s">
         <v>896</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
     </row>
     <row r="18" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>882</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="41" t="s">
         <v>865</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
     </row>
     <row r="19" spans="1:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>883</v>
       </c>
-      <c r="B19" s="33" t="s">
-        <v>897</v>
-      </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
+      <c r="B19" s="41" t="s">
+        <v>942</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
     </row>
     <row r="20" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>884</v>
       </c>
-      <c r="B20" s="33" t="s">
-        <v>928</v>
-      </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
+      <c r="B20" s="41" t="s">
+        <v>923</v>
+      </c>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
     </row>
     <row r="21" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
         <v>885</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="41" t="s">
         <v>866</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
     </row>
     <row r="22" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>886</v>
       </c>
-      <c r="B22" s="33" t="s">
-        <v>898</v>
-      </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
+      <c r="B22" s="41" t="s">
+        <v>941</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
     </row>
     <row r="23" spans="1:12" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
         <v>887</v>
       </c>
-      <c r="B23" s="33" t="s">
-        <v>899</v>
-      </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
+      <c r="B23" s="41" t="s">
+        <v>897</v>
+      </c>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
     </row>
     <row r="24" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
         <v>888</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="41" t="s">
         <v>867</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41"/>
     </row>
     <row r="25" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>902</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>915</v>
-      </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
+        <v>900</v>
+      </c>
+      <c r="B25" s="41" t="s">
+        <v>912</v>
+      </c>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
     </row>
     <row r="26" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>903</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>916</v>
-      </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
+        <v>901</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>913</v>
+      </c>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
     </row>
     <row r="27" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>914</v>
+      </c>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+    </row>
+    <row r="28" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>903</v>
+      </c>
+      <c r="B28" s="41" t="s">
+        <v>915</v>
+      </c>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+    </row>
+    <row r="29" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
         <v>904</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B29" s="41" t="s">
+        <v>940</v>
+      </c>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+    </row>
+    <row r="30" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>906</v>
+      </c>
+      <c r="B30" s="41" t="s">
+        <v>916</v>
+      </c>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+    </row>
+    <row r="31" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>910</v>
+      </c>
+      <c r="B31" s="41" t="s">
+        <v>921</v>
+      </c>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
+    </row>
+    <row r="32" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>907</v>
+      </c>
+      <c r="B32" s="41" t="s">
         <v>917</v>
       </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-    </row>
-    <row r="28" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
-        <v>905</v>
-      </c>
-      <c r="B28" s="33" t="s">
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>908</v>
+      </c>
+      <c r="B33" s="41" t="s">
         <v>918</v>
       </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-    </row>
-    <row r="29" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
-        <v>906</v>
-      </c>
-      <c r="B29" s="33" t="s">
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+    </row>
+    <row r="34" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>909</v>
+      </c>
+      <c r="B34" s="41" t="s">
         <v>919</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-    </row>
-    <row r="30" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
-        <v>907</v>
-      </c>
-      <c r="B30" s="33" t="s">
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+    </row>
+    <row r="35" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>911</v>
+      </c>
+      <c r="B35" s="41" t="s">
         <v>920</v>
       </c>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-    </row>
-    <row r="31" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
-        <v>909</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>921</v>
-      </c>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-    </row>
-    <row r="32" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
-        <v>913</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>926</v>
-      </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-    </row>
-    <row r="33" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
-        <v>910</v>
-      </c>
-      <c r="B33" s="33" t="s">
-        <v>922</v>
-      </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
-        <v>911</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>923</v>
-      </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-    </row>
-    <row r="35" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="28" t="s">
-        <v>912</v>
-      </c>
-      <c r="B35" s="33" t="s">
-        <v>924</v>
-      </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-    </row>
-    <row r="36" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
-        <v>914</v>
-      </c>
-      <c r="B36" s="33" t="s">
-        <v>925</v>
-      </c>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="B35:L35"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B29:L29"/>
-    <mergeCell ref="B30:L30"/>
-    <mergeCell ref="B31:L31"/>
-    <mergeCell ref="B32:L32"/>
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="B34:L34"/>
+  <mergeCells count="35">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="B19:L19"/>
+    <mergeCell ref="B20:L20"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="B23:L23"/>
+    <mergeCell ref="B24:L24"/>
+    <mergeCell ref="B25:L25"/>
+    <mergeCell ref="B26:L26"/>
+    <mergeCell ref="B27:L27"/>
     <mergeCell ref="B17:L17"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="B7:L7"/>
@@ -9391,22 +9374,14 @@
     <mergeCell ref="B15:L15"/>
     <mergeCell ref="B16:L16"/>
     <mergeCell ref="B11:L11"/>
+    <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B35:L35"/>
     <mergeCell ref="B28:L28"/>
-    <mergeCell ref="B18:L18"/>
-    <mergeCell ref="B19:L19"/>
-    <mergeCell ref="B20:L20"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B22:L22"/>
-    <mergeCell ref="B23:L23"/>
-    <mergeCell ref="B24:L24"/>
-    <mergeCell ref="B25:L25"/>
-    <mergeCell ref="B26:L26"/>
-    <mergeCell ref="B27:L27"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B29:L29"/>
+    <mergeCell ref="B30:L30"/>
+    <mergeCell ref="B31:L31"/>
+    <mergeCell ref="B32:L32"/>
+    <mergeCell ref="B33:L33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
